--- a/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>10393600</v>
+        <v>10564900</v>
       </c>
       <c r="E8" s="3">
-        <v>9354600</v>
+        <v>9508700</v>
       </c>
       <c r="F8" s="3">
-        <v>8816300</v>
+        <v>8961600</v>
       </c>
       <c r="G8" s="3">
-        <v>8843400</v>
+        <v>8989200</v>
       </c>
       <c r="H8" s="3">
-        <v>8805000</v>
+        <v>8950100</v>
       </c>
       <c r="I8" s="3">
-        <v>8365600</v>
+        <v>8503400</v>
       </c>
       <c r="J8" s="3">
-        <v>7884500</v>
+        <v>8014400</v>
       </c>
       <c r="K8" s="3">
         <v>7909500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1083400</v>
+        <v>1101300</v>
       </c>
       <c r="E9" s="3">
-        <v>1032200</v>
+        <v>1049200</v>
       </c>
       <c r="F9" s="3">
-        <v>1076900</v>
+        <v>1094600</v>
       </c>
       <c r="G9" s="3">
-        <v>1121100</v>
+        <v>1139500</v>
       </c>
       <c r="H9" s="3">
-        <v>870200</v>
+        <v>884600</v>
       </c>
       <c r="I9" s="3">
-        <v>831100</v>
+        <v>844800</v>
       </c>
       <c r="J9" s="3">
-        <v>817300</v>
+        <v>830700</v>
       </c>
       <c r="K9" s="3">
         <v>840600</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9310200</v>
+        <v>9463600</v>
       </c>
       <c r="E10" s="3">
-        <v>8322400</v>
+        <v>8459500</v>
       </c>
       <c r="F10" s="3">
-        <v>7739400</v>
+        <v>7867000</v>
       </c>
       <c r="G10" s="3">
-        <v>7722400</v>
+        <v>7849600</v>
       </c>
       <c r="H10" s="3">
-        <v>7934800</v>
+        <v>8065500</v>
       </c>
       <c r="I10" s="3">
-        <v>7534500</v>
+        <v>7658600</v>
       </c>
       <c r="J10" s="3">
-        <v>7067200</v>
+        <v>7183700</v>
       </c>
       <c r="K10" s="3">
         <v>7068900</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>45700</v>
+        <v>46400</v>
       </c>
       <c r="E14" s="3">
-        <v>23600</v>
+        <v>24000</v>
       </c>
       <c r="F14" s="3">
-        <v>12400</v>
+        <v>12600</v>
       </c>
       <c r="G14" s="3">
-        <v>181900</v>
+        <v>184900</v>
       </c>
       <c r="H14" s="3">
-        <v>56300</v>
+        <v>57200</v>
       </c>
       <c r="I14" s="3">
-        <v>100200</v>
+        <v>101900</v>
       </c>
       <c r="J14" s="3">
-        <v>71900</v>
+        <v>73100</v>
       </c>
       <c r="K14" s="3">
         <v>21500</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>41400</v>
+        <v>42100</v>
       </c>
       <c r="E15" s="3">
-        <v>35300</v>
+        <v>35900</v>
       </c>
       <c r="F15" s="3">
-        <v>44600</v>
+        <v>45400</v>
       </c>
       <c r="G15" s="3">
-        <v>40600</v>
+        <v>41300</v>
       </c>
       <c r="H15" s="3">
-        <v>46700</v>
+        <v>47500</v>
       </c>
       <c r="I15" s="3">
-        <v>51100</v>
+        <v>52000</v>
       </c>
       <c r="J15" s="3">
-        <v>41100</v>
+        <v>41700</v>
       </c>
       <c r="K15" s="3">
         <v>40000</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8795700</v>
+        <v>8940600</v>
       </c>
       <c r="E17" s="3">
-        <v>7924600</v>
+        <v>8055200</v>
       </c>
       <c r="F17" s="3">
-        <v>7480100</v>
+        <v>7603300</v>
       </c>
       <c r="G17" s="3">
-        <v>7741100</v>
+        <v>7868700</v>
       </c>
       <c r="H17" s="3">
-        <v>7585800</v>
+        <v>7710800</v>
       </c>
       <c r="I17" s="3">
-        <v>7282300</v>
+        <v>7402300</v>
       </c>
       <c r="J17" s="3">
-        <v>6853600</v>
+        <v>6966600</v>
       </c>
       <c r="K17" s="3">
         <v>6833900</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1597900</v>
+        <v>1624200</v>
       </c>
       <c r="E18" s="3">
-        <v>1430000</v>
+        <v>1453600</v>
       </c>
       <c r="F18" s="3">
-        <v>1336200</v>
+        <v>1358300</v>
       </c>
       <c r="G18" s="3">
-        <v>1102300</v>
+        <v>1120500</v>
       </c>
       <c r="H18" s="3">
-        <v>1219200</v>
+        <v>1239200</v>
       </c>
       <c r="I18" s="3">
-        <v>1083200</v>
+        <v>1101100</v>
       </c>
       <c r="J18" s="3">
-        <v>1030800</v>
+        <v>1047800</v>
       </c>
       <c r="K18" s="3">
         <v>1075600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1968900</v>
+        <v>2001000</v>
       </c>
       <c r="E21" s="3">
-        <v>1771100</v>
+        <v>1800000</v>
       </c>
       <c r="F21" s="3">
-        <v>1704700</v>
+        <v>1732500</v>
       </c>
       <c r="G21" s="3">
-        <v>1515900</v>
+        <v>1540500</v>
       </c>
       <c r="H21" s="3">
-        <v>1506000</v>
+        <v>1530500</v>
       </c>
       <c r="I21" s="3">
-        <v>1370300</v>
+        <v>1392600</v>
       </c>
       <c r="J21" s="3">
-        <v>1306600</v>
+        <v>1327900</v>
       </c>
       <c r="K21" s="3">
         <v>1371800</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1597900</v>
+        <v>1624200</v>
       </c>
       <c r="E23" s="3">
-        <v>1430000</v>
+        <v>1453600</v>
       </c>
       <c r="F23" s="3">
-        <v>1336200</v>
+        <v>1358300</v>
       </c>
       <c r="G23" s="3">
-        <v>1102300</v>
+        <v>1120500</v>
       </c>
       <c r="H23" s="3">
-        <v>1219200</v>
+        <v>1239200</v>
       </c>
       <c r="I23" s="3">
-        <v>1083200</v>
+        <v>1101100</v>
       </c>
       <c r="J23" s="3">
-        <v>1030800</v>
+        <v>1047800</v>
       </c>
       <c r="K23" s="3">
         <v>1075600</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>412000</v>
+        <v>418800</v>
       </c>
       <c r="E24" s="3">
-        <v>364100</v>
+        <v>370100</v>
       </c>
       <c r="F24" s="3">
-        <v>340900</v>
+        <v>346500</v>
       </c>
       <c r="G24" s="3">
-        <v>289600</v>
+        <v>294400</v>
       </c>
       <c r="H24" s="3">
-        <v>300800</v>
+        <v>305800</v>
       </c>
       <c r="I24" s="3">
-        <v>253400</v>
+        <v>257600</v>
       </c>
       <c r="J24" s="3">
-        <v>278200</v>
+        <v>282800</v>
       </c>
       <c r="K24" s="3">
         <v>284300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1185900</v>
+        <v>1205500</v>
       </c>
       <c r="E26" s="3">
-        <v>1065900</v>
+        <v>1083500</v>
       </c>
       <c r="F26" s="3">
-        <v>995300</v>
+        <v>1011700</v>
       </c>
       <c r="G26" s="3">
-        <v>812700</v>
+        <v>826100</v>
       </c>
       <c r="H26" s="3">
-        <v>918400</v>
+        <v>933500</v>
       </c>
       <c r="I26" s="3">
-        <v>829800</v>
+        <v>843500</v>
       </c>
       <c r="J26" s="3">
-        <v>752600</v>
+        <v>765000</v>
       </c>
       <c r="K26" s="3">
         <v>791200</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1185900</v>
+        <v>1205500</v>
       </c>
       <c r="E27" s="3">
-        <v>1065900</v>
+        <v>1083500</v>
       </c>
       <c r="F27" s="3">
-        <v>995300</v>
+        <v>1011700</v>
       </c>
       <c r="G27" s="3">
-        <v>812700</v>
+        <v>826100</v>
       </c>
       <c r="H27" s="3">
-        <v>918400</v>
+        <v>933500</v>
       </c>
       <c r="I27" s="3">
-        <v>829800</v>
+        <v>843500</v>
       </c>
       <c r="J27" s="3">
-        <v>752600</v>
+        <v>765000</v>
       </c>
       <c r="K27" s="3">
         <v>791200</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1185900</v>
+        <v>1205500</v>
       </c>
       <c r="E33" s="3">
-        <v>1065900</v>
+        <v>1083500</v>
       </c>
       <c r="F33" s="3">
-        <v>995300</v>
+        <v>1011700</v>
       </c>
       <c r="G33" s="3">
-        <v>812700</v>
+        <v>826100</v>
       </c>
       <c r="H33" s="3">
-        <v>918400</v>
+        <v>933500</v>
       </c>
       <c r="I33" s="3">
-        <v>829800</v>
+        <v>843500</v>
       </c>
       <c r="J33" s="3">
-        <v>752600</v>
+        <v>765000</v>
       </c>
       <c r="K33" s="3">
         <v>791200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1185900</v>
+        <v>1205500</v>
       </c>
       <c r="E35" s="3">
-        <v>1065900</v>
+        <v>1083500</v>
       </c>
       <c r="F35" s="3">
-        <v>995300</v>
+        <v>1011700</v>
       </c>
       <c r="G35" s="3">
-        <v>812700</v>
+        <v>826100</v>
       </c>
       <c r="H35" s="3">
-        <v>918400</v>
+        <v>933500</v>
       </c>
       <c r="I35" s="3">
-        <v>829800</v>
+        <v>843500</v>
       </c>
       <c r="J35" s="3">
-        <v>752600</v>
+        <v>765000</v>
       </c>
       <c r="K35" s="3">
         <v>791200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1140200</v>
+        <v>1159000</v>
       </c>
       <c r="E41" s="3">
-        <v>702600</v>
+        <v>714200</v>
       </c>
       <c r="F41" s="3">
-        <v>1235300</v>
+        <v>1255700</v>
       </c>
       <c r="G41" s="3">
-        <v>1241700</v>
+        <v>1262200</v>
       </c>
       <c r="H41" s="3">
-        <v>155500</v>
+        <v>158000</v>
       </c>
       <c r="I41" s="3">
-        <v>133800</v>
+        <v>136000</v>
       </c>
       <c r="J41" s="3">
-        <v>120600</v>
+        <v>122600</v>
       </c>
       <c r="K41" s="3">
         <v>441600</v>
@@ -2038,7 +2038,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>58200</v>
+        <v>59100</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>8</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1141500</v>
+        <v>1160300</v>
       </c>
       <c r="E43" s="3">
-        <v>1063500</v>
+        <v>1081000</v>
       </c>
       <c r="F43" s="3">
-        <v>898900</v>
+        <v>913700</v>
       </c>
       <c r="G43" s="3">
-        <v>907800</v>
+        <v>922800</v>
       </c>
       <c r="H43" s="3">
-        <v>994000</v>
+        <v>1010400</v>
       </c>
       <c r="I43" s="3">
-        <v>1080300</v>
+        <v>1098100</v>
       </c>
       <c r="J43" s="3">
-        <v>939600</v>
+        <v>955100</v>
       </c>
       <c r="K43" s="3">
         <v>821400</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>831500</v>
+        <v>845200</v>
       </c>
       <c r="E44" s="3">
-        <v>866500</v>
+        <v>880800</v>
       </c>
       <c r="F44" s="3">
-        <v>759800</v>
+        <v>772300</v>
       </c>
       <c r="G44" s="3">
-        <v>781700</v>
+        <v>794600</v>
       </c>
       <c r="H44" s="3">
-        <v>796800</v>
+        <v>810000</v>
       </c>
       <c r="I44" s="3">
-        <v>685400</v>
+        <v>696700</v>
       </c>
       <c r="J44" s="3">
-        <v>670800</v>
+        <v>681800</v>
       </c>
       <c r="K44" s="3">
         <v>692600</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>415600</v>
+        <v>422400</v>
       </c>
       <c r="E45" s="3">
-        <v>529200</v>
+        <v>537900</v>
       </c>
       <c r="F45" s="3">
-        <v>570300</v>
+        <v>579700</v>
       </c>
       <c r="G45" s="3">
-        <v>657300</v>
+        <v>668100</v>
       </c>
       <c r="H45" s="3">
-        <v>421800</v>
+        <v>428800</v>
       </c>
       <c r="I45" s="3">
-        <v>357300</v>
+        <v>363200</v>
       </c>
       <c r="J45" s="3">
-        <v>350500</v>
+        <v>356300</v>
       </c>
       <c r="K45" s="3">
         <v>416200</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3586900</v>
+        <v>3646000</v>
       </c>
       <c r="E46" s="3">
-        <v>3161800</v>
+        <v>3213900</v>
       </c>
       <c r="F46" s="3">
-        <v>3464300</v>
+        <v>3521400</v>
       </c>
       <c r="G46" s="3">
-        <v>3588500</v>
+        <v>3647600</v>
       </c>
       <c r="H46" s="3">
-        <v>2368200</v>
+        <v>2407200</v>
       </c>
       <c r="I46" s="3">
-        <v>2257000</v>
+        <v>2294100</v>
       </c>
       <c r="J46" s="3">
-        <v>2081400</v>
+        <v>2115700</v>
       </c>
       <c r="K46" s="3">
         <v>2371900</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>27500</v>
+        <v>28000</v>
       </c>
       <c r="E47" s="3">
-        <v>19900</v>
+        <v>20300</v>
       </c>
       <c r="F47" s="3">
-        <v>111000</v>
+        <v>112800</v>
       </c>
       <c r="G47" s="3">
-        <v>113800</v>
+        <v>115700</v>
       </c>
       <c r="H47" s="3">
-        <v>128600</v>
+        <v>130700</v>
       </c>
       <c r="I47" s="3">
-        <v>85600</v>
+        <v>87000</v>
       </c>
       <c r="J47" s="3">
-        <v>80900</v>
+        <v>82300</v>
       </c>
       <c r="K47" s="3">
         <v>95800</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>633700</v>
+        <v>644100</v>
       </c>
       <c r="E48" s="3">
-        <v>657700</v>
+        <v>668600</v>
       </c>
       <c r="F48" s="3">
-        <v>682200</v>
+        <v>693400</v>
       </c>
       <c r="G48" s="3">
-        <v>756000</v>
+        <v>768400</v>
       </c>
       <c r="H48" s="3">
-        <v>289100</v>
+        <v>293900</v>
       </c>
       <c r="I48" s="3">
-        <v>282100</v>
+        <v>286800</v>
       </c>
       <c r="J48" s="3">
-        <v>288300</v>
+        <v>293100</v>
       </c>
       <c r="K48" s="3">
         <v>325200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7020000</v>
+        <v>7135700</v>
       </c>
       <c r="E49" s="3">
-        <v>6804100</v>
+        <v>6916200</v>
       </c>
       <c r="F49" s="3">
-        <v>6453700</v>
+        <v>6560100</v>
       </c>
       <c r="G49" s="3">
-        <v>6645400</v>
+        <v>6754900</v>
       </c>
       <c r="H49" s="3">
-        <v>6186000</v>
+        <v>6287900</v>
       </c>
       <c r="I49" s="3">
-        <v>5862700</v>
+        <v>5959400</v>
       </c>
       <c r="J49" s="3">
-        <v>5666000</v>
+        <v>5759300</v>
       </c>
       <c r="K49" s="3">
         <v>5666800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>218300</v>
+        <v>221900</v>
       </c>
       <c r="E52" s="3">
-        <v>389100</v>
+        <v>395500</v>
       </c>
       <c r="F52" s="3">
-        <v>209300</v>
+        <v>212700</v>
       </c>
       <c r="G52" s="3">
-        <v>201500</v>
+        <v>204900</v>
       </c>
       <c r="H52" s="3">
-        <v>204300</v>
+        <v>207700</v>
       </c>
       <c r="I52" s="3">
-        <v>177800</v>
+        <v>180800</v>
       </c>
       <c r="J52" s="3">
-        <v>168500</v>
+        <v>171300</v>
       </c>
       <c r="K52" s="3">
         <v>197600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11486400</v>
+        <v>11675700</v>
       </c>
       <c r="E54" s="3">
-        <v>11032700</v>
+        <v>11214500</v>
       </c>
       <c r="F54" s="3">
-        <v>10920400</v>
+        <v>11100400</v>
       </c>
       <c r="G54" s="3">
-        <v>11305300</v>
+        <v>11491600</v>
       </c>
       <c r="H54" s="3">
-        <v>9176100</v>
+        <v>9327300</v>
       </c>
       <c r="I54" s="3">
-        <v>8665300</v>
+        <v>8808100</v>
       </c>
       <c r="J54" s="3">
-        <v>8285200</v>
+        <v>8421700</v>
       </c>
       <c r="K54" s="3">
         <v>8657300</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>672200</v>
+        <v>683300</v>
       </c>
       <c r="E57" s="3">
-        <v>738900</v>
+        <v>751100</v>
       </c>
       <c r="F57" s="3">
-        <v>648000</v>
+        <v>658700</v>
       </c>
       <c r="G57" s="3">
-        <v>745900</v>
+        <v>758200</v>
       </c>
       <c r="H57" s="3">
-        <v>806200</v>
+        <v>819500</v>
       </c>
       <c r="I57" s="3">
-        <v>825000</v>
+        <v>838600</v>
       </c>
       <c r="J57" s="3">
-        <v>730100</v>
+        <v>742200</v>
       </c>
       <c r="K57" s="3">
         <v>820200</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>987200</v>
+        <v>1003400</v>
       </c>
       <c r="E58" s="3">
-        <v>182800</v>
+        <v>185800</v>
       </c>
       <c r="F58" s="3">
-        <v>407500</v>
+        <v>414200</v>
       </c>
       <c r="G58" s="3">
-        <v>355900</v>
+        <v>361700</v>
       </c>
       <c r="H58" s="3">
-        <v>82500</v>
+        <v>83900</v>
       </c>
       <c r="I58" s="3">
-        <v>253400</v>
+        <v>257600</v>
       </c>
       <c r="J58" s="3">
-        <v>89000</v>
+        <v>90500</v>
       </c>
       <c r="K58" s="3">
         <v>142200</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1718200</v>
+        <v>1746500</v>
       </c>
       <c r="E59" s="3">
-        <v>1731400</v>
+        <v>1759900</v>
       </c>
       <c r="F59" s="3">
-        <v>1709600</v>
+        <v>1737800</v>
       </c>
       <c r="G59" s="3">
-        <v>1556100</v>
+        <v>1581700</v>
       </c>
       <c r="H59" s="3">
-        <v>1208100</v>
+        <v>1228000</v>
       </c>
       <c r="I59" s="3">
-        <v>1189600</v>
+        <v>1209200</v>
       </c>
       <c r="J59" s="3">
-        <v>1144900</v>
+        <v>1163700</v>
       </c>
       <c r="K59" s="3">
         <v>1094800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3377500</v>
+        <v>3433200</v>
       </c>
       <c r="E60" s="3">
-        <v>2653100</v>
+        <v>2696800</v>
       </c>
       <c r="F60" s="3">
-        <v>2765200</v>
+        <v>2810700</v>
       </c>
       <c r="G60" s="3">
-        <v>2657800</v>
+        <v>2701600</v>
       </c>
       <c r="H60" s="3">
-        <v>2096800</v>
+        <v>2131300</v>
       </c>
       <c r="I60" s="3">
-        <v>2268000</v>
+        <v>2305400</v>
       </c>
       <c r="J60" s="3">
-        <v>1964100</v>
+        <v>1996400</v>
       </c>
       <c r="K60" s="3">
         <v>2057200</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1733500</v>
+        <v>1762100</v>
       </c>
       <c r="E61" s="3">
-        <v>2708000</v>
+        <v>2752600</v>
       </c>
       <c r="F61" s="3">
-        <v>2630400</v>
+        <v>2673700</v>
       </c>
       <c r="G61" s="3">
-        <v>2889100</v>
+        <v>2936700</v>
       </c>
       <c r="H61" s="3">
-        <v>1612300</v>
+        <v>1638900</v>
       </c>
       <c r="I61" s="3">
-        <v>1055800</v>
+        <v>1073200</v>
       </c>
       <c r="J61" s="3">
-        <v>1264700</v>
+        <v>1285500</v>
       </c>
       <c r="K61" s="3">
         <v>1272600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>333700</v>
+        <v>339200</v>
       </c>
       <c r="E62" s="3">
-        <v>384200</v>
+        <v>390600</v>
       </c>
       <c r="F62" s="3">
-        <v>445900</v>
+        <v>453200</v>
       </c>
       <c r="G62" s="3">
-        <v>477200</v>
+        <v>485100</v>
       </c>
       <c r="H62" s="3">
-        <v>462300</v>
+        <v>469900</v>
       </c>
       <c r="I62" s="3">
-        <v>481500</v>
+        <v>489400</v>
       </c>
       <c r="J62" s="3">
-        <v>547100</v>
+        <v>556100</v>
       </c>
       <c r="K62" s="3">
         <v>541300</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5444700</v>
+        <v>5534400</v>
       </c>
       <c r="E66" s="3">
-        <v>5745300</v>
+        <v>5840000</v>
       </c>
       <c r="F66" s="3">
-        <v>5841400</v>
+        <v>5937600</v>
       </c>
       <c r="G66" s="3">
-        <v>6024100</v>
+        <v>6123400</v>
       </c>
       <c r="H66" s="3">
-        <v>4171300</v>
+        <v>4240100</v>
       </c>
       <c r="I66" s="3">
-        <v>3805400</v>
+        <v>3868100</v>
       </c>
       <c r="J66" s="3">
-        <v>3775800</v>
+        <v>3838000</v>
       </c>
       <c r="K66" s="3">
         <v>3871100</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4601300</v>
+        <v>4677100</v>
       </c>
       <c r="E72" s="3">
-        <v>3944000</v>
+        <v>4009000</v>
       </c>
       <c r="F72" s="3">
-        <v>3440400</v>
+        <v>3497100</v>
       </c>
       <c r="G72" s="3">
-        <v>3419600</v>
+        <v>3475900</v>
       </c>
       <c r="H72" s="3">
-        <v>3313600</v>
+        <v>3368200</v>
       </c>
       <c r="I72" s="3">
-        <v>3090800</v>
+        <v>3141800</v>
       </c>
       <c r="J72" s="3">
-        <v>2758600</v>
+        <v>2804100</v>
       </c>
       <c r="K72" s="3">
         <v>2797700</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6041700</v>
+        <v>6141200</v>
       </c>
       <c r="E76" s="3">
-        <v>5287300</v>
+        <v>5374500</v>
       </c>
       <c r="F76" s="3">
-        <v>5079100</v>
+        <v>5162800</v>
       </c>
       <c r="G76" s="3">
-        <v>5281100</v>
+        <v>5368100</v>
       </c>
       <c r="H76" s="3">
-        <v>5004800</v>
+        <v>5087300</v>
       </c>
       <c r="I76" s="3">
-        <v>4859900</v>
+        <v>4940000</v>
       </c>
       <c r="J76" s="3">
-        <v>4509400</v>
+        <v>4583700</v>
       </c>
       <c r="K76" s="3">
         <v>4786100</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1185900</v>
+        <v>1205500</v>
       </c>
       <c r="E81" s="3">
-        <v>1065900</v>
+        <v>1083500</v>
       </c>
       <c r="F81" s="3">
-        <v>995300</v>
+        <v>1011700</v>
       </c>
       <c r="G81" s="3">
-        <v>812700</v>
+        <v>826100</v>
       </c>
       <c r="H81" s="3">
-        <v>918400</v>
+        <v>933500</v>
       </c>
       <c r="I81" s="3">
-        <v>829800</v>
+        <v>843500</v>
       </c>
       <c r="J81" s="3">
-        <v>752600</v>
+        <v>765000</v>
       </c>
       <c r="K81" s="3">
         <v>791200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>368900</v>
+        <v>375000</v>
       </c>
       <c r="E83" s="3">
-        <v>339200</v>
+        <v>344800</v>
       </c>
       <c r="F83" s="3">
-        <v>366400</v>
+        <v>372500</v>
       </c>
       <c r="G83" s="3">
-        <v>411300</v>
+        <v>418000</v>
       </c>
       <c r="H83" s="3">
-        <v>285200</v>
+        <v>289900</v>
       </c>
       <c r="I83" s="3">
-        <v>285500</v>
+        <v>290200</v>
       </c>
       <c r="J83" s="3">
-        <v>274200</v>
+        <v>278700</v>
       </c>
       <c r="K83" s="3">
         <v>296200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1535600</v>
+        <v>1560900</v>
       </c>
       <c r="E89" s="3">
-        <v>1355900</v>
+        <v>1378200</v>
       </c>
       <c r="F89" s="3">
-        <v>1538300</v>
+        <v>1563600</v>
       </c>
       <c r="G89" s="3">
-        <v>1409300</v>
+        <v>1432600</v>
       </c>
       <c r="H89" s="3">
-        <v>1187900</v>
+        <v>1207400</v>
       </c>
       <c r="I89" s="3">
-        <v>1085700</v>
+        <v>1103600</v>
       </c>
       <c r="J89" s="3">
-        <v>987700</v>
+        <v>1004000</v>
       </c>
       <c r="K89" s="3">
         <v>987000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-116200</v>
+        <v>-118100</v>
       </c>
       <c r="E91" s="3">
-        <v>-113500</v>
+        <v>-115400</v>
       </c>
       <c r="F91" s="3">
-        <v>-88600</v>
+        <v>-90000</v>
       </c>
       <c r="G91" s="3">
-        <v>-93400</v>
+        <v>-94900</v>
       </c>
       <c r="H91" s="3">
-        <v>-117800</v>
+        <v>-119800</v>
       </c>
       <c r="I91" s="3">
-        <v>-104100</v>
+        <v>-105900</v>
       </c>
       <c r="J91" s="3">
-        <v>-81900</v>
+        <v>-83300</v>
       </c>
       <c r="K91" s="3">
         <v>-122500</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-408500</v>
+        <v>-415200</v>
       </c>
       <c r="E94" s="3">
-        <v>-663000</v>
+        <v>-673900</v>
       </c>
       <c r="F94" s="3">
-        <v>-289000</v>
+        <v>-293800</v>
       </c>
       <c r="G94" s="3">
-        <v>-416200</v>
+        <v>-423000</v>
       </c>
       <c r="H94" s="3">
-        <v>-691200</v>
+        <v>-702600</v>
       </c>
       <c r="I94" s="3">
-        <v>-419800</v>
+        <v>-426700</v>
       </c>
       <c r="J94" s="3">
-        <v>-430600</v>
+        <v>-437700</v>
       </c>
       <c r="K94" s="3">
         <v>-283400</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-866900</v>
+        <v>-881200</v>
       </c>
       <c r="E100" s="3">
-        <v>-1156700</v>
+        <v>-1175800</v>
       </c>
       <c r="F100" s="3">
-        <v>-1201900</v>
+        <v>-1221800</v>
       </c>
       <c r="G100" s="3">
-        <v>68500</v>
+        <v>69600</v>
       </c>
       <c r="H100" s="3">
-        <v>-457400</v>
+        <v>-464900</v>
       </c>
       <c r="I100" s="3">
-        <v>-639100</v>
+        <v>-649600</v>
       </c>
       <c r="J100" s="3">
-        <v>-860000</v>
+        <v>-874200</v>
       </c>
       <c r="K100" s="3">
         <v>-493300</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>6500</v>
+        <v>6600</v>
       </c>
       <c r="E101" s="3">
-        <v>-33800</v>
+        <v>-34400</v>
       </c>
       <c r="F101" s="3">
-        <v>-53700</v>
+        <v>-54600</v>
       </c>
       <c r="G101" s="3">
-        <v>24600</v>
+        <v>25000</v>
       </c>
       <c r="H101" s="3">
-        <v>-17600</v>
+        <v>-17900</v>
       </c>
       <c r="I101" s="3">
-        <v>-13600</v>
+        <v>-13800</v>
       </c>
       <c r="J101" s="3">
-        <v>-10200</v>
+        <v>-10300</v>
       </c>
       <c r="K101" s="3">
         <v>5400</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>266700</v>
+        <v>271100</v>
       </c>
       <c r="E102" s="3">
-        <v>-497700</v>
+        <v>-505900</v>
       </c>
       <c r="F102" s="3">
-        <v>-6400</v>
+        <v>-6500</v>
       </c>
       <c r="G102" s="3">
-        <v>1086300</v>
+        <v>1104200</v>
       </c>
       <c r="H102" s="3">
-        <v>21600</v>
+        <v>22000</v>
       </c>
       <c r="I102" s="3">
-        <v>13200</v>
+        <v>13500</v>
       </c>
       <c r="J102" s="3">
-        <v>-313100</v>
+        <v>-318300</v>
       </c>
       <c r="K102" s="3">
         <v>215600</v>

--- a/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>10564900</v>
+        <v>10418600</v>
       </c>
       <c r="E8" s="3">
-        <v>9508700</v>
+        <v>9377100</v>
       </c>
       <c r="F8" s="3">
-        <v>8961600</v>
+        <v>8837500</v>
       </c>
       <c r="G8" s="3">
-        <v>8989200</v>
+        <v>8864700</v>
       </c>
       <c r="H8" s="3">
-        <v>8950100</v>
+        <v>8826200</v>
       </c>
       <c r="I8" s="3">
-        <v>8503400</v>
+        <v>8385700</v>
       </c>
       <c r="J8" s="3">
-        <v>8014400</v>
+        <v>7903500</v>
       </c>
       <c r="K8" s="3">
         <v>7909500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1101300</v>
+        <v>1086000</v>
       </c>
       <c r="E9" s="3">
-        <v>1049200</v>
+        <v>1034700</v>
       </c>
       <c r="F9" s="3">
-        <v>1094600</v>
+        <v>1079500</v>
       </c>
       <c r="G9" s="3">
-        <v>1139500</v>
+        <v>1123800</v>
       </c>
       <c r="H9" s="3">
-        <v>884600</v>
+        <v>872300</v>
       </c>
       <c r="I9" s="3">
-        <v>844800</v>
+        <v>833100</v>
       </c>
       <c r="J9" s="3">
-        <v>830700</v>
+        <v>819200</v>
       </c>
       <c r="K9" s="3">
         <v>840600</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9463600</v>
+        <v>9332600</v>
       </c>
       <c r="E10" s="3">
-        <v>8459500</v>
+        <v>8342400</v>
       </c>
       <c r="F10" s="3">
-        <v>7867000</v>
+        <v>7758100</v>
       </c>
       <c r="G10" s="3">
-        <v>7849600</v>
+        <v>7741000</v>
       </c>
       <c r="H10" s="3">
-        <v>8065500</v>
+        <v>7953900</v>
       </c>
       <c r="I10" s="3">
-        <v>7658600</v>
+        <v>7552600</v>
       </c>
       <c r="J10" s="3">
-        <v>7183700</v>
+        <v>7084200</v>
       </c>
       <c r="K10" s="3">
         <v>7068900</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>46400</v>
+        <v>45800</v>
       </c>
       <c r="E14" s="3">
-        <v>24000</v>
+        <v>23700</v>
       </c>
       <c r="F14" s="3">
-        <v>12600</v>
+        <v>12400</v>
       </c>
       <c r="G14" s="3">
-        <v>184900</v>
+        <v>182300</v>
       </c>
       <c r="H14" s="3">
-        <v>57200</v>
+        <v>56400</v>
       </c>
       <c r="I14" s="3">
-        <v>101900</v>
+        <v>100500</v>
       </c>
       <c r="J14" s="3">
-        <v>73100</v>
+        <v>72100</v>
       </c>
       <c r="K14" s="3">
         <v>21500</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>42100</v>
+        <v>41500</v>
       </c>
       <c r="E15" s="3">
-        <v>35900</v>
+        <v>35400</v>
       </c>
       <c r="F15" s="3">
-        <v>45400</v>
+        <v>44700</v>
       </c>
       <c r="G15" s="3">
-        <v>41300</v>
+        <v>40700</v>
       </c>
       <c r="H15" s="3">
-        <v>47500</v>
+        <v>46800</v>
       </c>
       <c r="I15" s="3">
-        <v>52000</v>
+        <v>51200</v>
       </c>
       <c r="J15" s="3">
-        <v>41700</v>
+        <v>41200</v>
       </c>
       <c r="K15" s="3">
         <v>40000</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8940600</v>
+        <v>8816900</v>
       </c>
       <c r="E17" s="3">
-        <v>8055200</v>
+        <v>7943700</v>
       </c>
       <c r="F17" s="3">
-        <v>7603300</v>
+        <v>7498100</v>
       </c>
       <c r="G17" s="3">
-        <v>7868700</v>
+        <v>7759700</v>
       </c>
       <c r="H17" s="3">
-        <v>7710800</v>
+        <v>7604100</v>
       </c>
       <c r="I17" s="3">
-        <v>7402300</v>
+        <v>7299900</v>
       </c>
       <c r="J17" s="3">
-        <v>6966600</v>
+        <v>6870100</v>
       </c>
       <c r="K17" s="3">
         <v>6833900</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1624200</v>
+        <v>1601800</v>
       </c>
       <c r="E18" s="3">
-        <v>1453600</v>
+        <v>1433400</v>
       </c>
       <c r="F18" s="3">
-        <v>1358300</v>
+        <v>1339500</v>
       </c>
       <c r="G18" s="3">
-        <v>1120500</v>
+        <v>1105000</v>
       </c>
       <c r="H18" s="3">
-        <v>1239200</v>
+        <v>1222100</v>
       </c>
       <c r="I18" s="3">
-        <v>1101100</v>
+        <v>1085800</v>
       </c>
       <c r="J18" s="3">
-        <v>1047800</v>
+        <v>1033300</v>
       </c>
       <c r="K18" s="3">
         <v>1075600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2001000</v>
+        <v>1970600</v>
       </c>
       <c r="E21" s="3">
-        <v>1800000</v>
+        <v>1772600</v>
       </c>
       <c r="F21" s="3">
-        <v>1732500</v>
+        <v>1705800</v>
       </c>
       <c r="G21" s="3">
-        <v>1540500</v>
+        <v>1516200</v>
       </c>
       <c r="H21" s="3">
-        <v>1530500</v>
+        <v>1507300</v>
       </c>
       <c r="I21" s="3">
-        <v>1392600</v>
+        <v>1371300</v>
       </c>
       <c r="J21" s="3">
-        <v>1327900</v>
+        <v>1307500</v>
       </c>
       <c r="K21" s="3">
         <v>1371800</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1624200</v>
+        <v>1601800</v>
       </c>
       <c r="E23" s="3">
-        <v>1453600</v>
+        <v>1433400</v>
       </c>
       <c r="F23" s="3">
-        <v>1358300</v>
+        <v>1339500</v>
       </c>
       <c r="G23" s="3">
-        <v>1120500</v>
+        <v>1105000</v>
       </c>
       <c r="H23" s="3">
-        <v>1239200</v>
+        <v>1222100</v>
       </c>
       <c r="I23" s="3">
-        <v>1101100</v>
+        <v>1085800</v>
       </c>
       <c r="J23" s="3">
-        <v>1047800</v>
+        <v>1033300</v>
       </c>
       <c r="K23" s="3">
         <v>1075600</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>418800</v>
+        <v>413000</v>
       </c>
       <c r="E24" s="3">
-        <v>370100</v>
+        <v>365000</v>
       </c>
       <c r="F24" s="3">
-        <v>346500</v>
+        <v>341700</v>
       </c>
       <c r="G24" s="3">
-        <v>294400</v>
+        <v>290300</v>
       </c>
       <c r="H24" s="3">
-        <v>305800</v>
+        <v>301500</v>
       </c>
       <c r="I24" s="3">
-        <v>257600</v>
+        <v>254000</v>
       </c>
       <c r="J24" s="3">
-        <v>282800</v>
+        <v>278900</v>
       </c>
       <c r="K24" s="3">
         <v>284300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1205500</v>
+        <v>1188800</v>
       </c>
       <c r="E26" s="3">
-        <v>1083500</v>
+        <v>1068500</v>
       </c>
       <c r="F26" s="3">
-        <v>1011700</v>
+        <v>997700</v>
       </c>
       <c r="G26" s="3">
-        <v>826100</v>
+        <v>814700</v>
       </c>
       <c r="H26" s="3">
-        <v>933500</v>
+        <v>920600</v>
       </c>
       <c r="I26" s="3">
-        <v>843500</v>
+        <v>831800</v>
       </c>
       <c r="J26" s="3">
-        <v>765000</v>
+        <v>754400</v>
       </c>
       <c r="K26" s="3">
         <v>791200</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1205500</v>
+        <v>1188800</v>
       </c>
       <c r="E27" s="3">
-        <v>1083500</v>
+        <v>1068500</v>
       </c>
       <c r="F27" s="3">
-        <v>1011700</v>
+        <v>997700</v>
       </c>
       <c r="G27" s="3">
-        <v>826100</v>
+        <v>814700</v>
       </c>
       <c r="H27" s="3">
-        <v>933500</v>
+        <v>920600</v>
       </c>
       <c r="I27" s="3">
-        <v>843500</v>
+        <v>831800</v>
       </c>
       <c r="J27" s="3">
-        <v>765000</v>
+        <v>754400</v>
       </c>
       <c r="K27" s="3">
         <v>791200</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1205500</v>
+        <v>1188800</v>
       </c>
       <c r="E33" s="3">
-        <v>1083500</v>
+        <v>1068500</v>
       </c>
       <c r="F33" s="3">
-        <v>1011700</v>
+        <v>997700</v>
       </c>
       <c r="G33" s="3">
-        <v>826100</v>
+        <v>814700</v>
       </c>
       <c r="H33" s="3">
-        <v>933500</v>
+        <v>920600</v>
       </c>
       <c r="I33" s="3">
-        <v>843500</v>
+        <v>831800</v>
       </c>
       <c r="J33" s="3">
-        <v>765000</v>
+        <v>754400</v>
       </c>
       <c r="K33" s="3">
         <v>791200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1205500</v>
+        <v>1188800</v>
       </c>
       <c r="E35" s="3">
-        <v>1083500</v>
+        <v>1068500</v>
       </c>
       <c r="F35" s="3">
-        <v>1011700</v>
+        <v>997700</v>
       </c>
       <c r="G35" s="3">
-        <v>826100</v>
+        <v>814700</v>
       </c>
       <c r="H35" s="3">
-        <v>933500</v>
+        <v>920600</v>
       </c>
       <c r="I35" s="3">
-        <v>843500</v>
+        <v>831800</v>
       </c>
       <c r="J35" s="3">
-        <v>765000</v>
+        <v>754400</v>
       </c>
       <c r="K35" s="3">
         <v>791200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1159000</v>
+        <v>1142900</v>
       </c>
       <c r="E41" s="3">
-        <v>714200</v>
+        <v>704300</v>
       </c>
       <c r="F41" s="3">
-        <v>1255700</v>
+        <v>1238300</v>
       </c>
       <c r="G41" s="3">
-        <v>1262200</v>
+        <v>1244700</v>
       </c>
       <c r="H41" s="3">
-        <v>158000</v>
+        <v>155800</v>
       </c>
       <c r="I41" s="3">
-        <v>136000</v>
+        <v>134200</v>
       </c>
       <c r="J41" s="3">
-        <v>122600</v>
+        <v>120900</v>
       </c>
       <c r="K41" s="3">
         <v>441600</v>
@@ -2038,7 +2038,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>59100</v>
+        <v>58300</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>8</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1160300</v>
+        <v>1144200</v>
       </c>
       <c r="E43" s="3">
-        <v>1081000</v>
+        <v>1066000</v>
       </c>
       <c r="F43" s="3">
-        <v>913700</v>
+        <v>901000</v>
       </c>
       <c r="G43" s="3">
-        <v>922800</v>
+        <v>910000</v>
       </c>
       <c r="H43" s="3">
-        <v>1010400</v>
+        <v>996400</v>
       </c>
       <c r="I43" s="3">
-        <v>1098100</v>
+        <v>1082900</v>
       </c>
       <c r="J43" s="3">
-        <v>955100</v>
+        <v>941900</v>
       </c>
       <c r="K43" s="3">
         <v>821400</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>845200</v>
+        <v>833500</v>
       </c>
       <c r="E44" s="3">
-        <v>880800</v>
+        <v>868600</v>
       </c>
       <c r="F44" s="3">
-        <v>772300</v>
+        <v>761600</v>
       </c>
       <c r="G44" s="3">
-        <v>794600</v>
+        <v>783600</v>
       </c>
       <c r="H44" s="3">
-        <v>810000</v>
+        <v>798700</v>
       </c>
       <c r="I44" s="3">
-        <v>696700</v>
+        <v>687100</v>
       </c>
       <c r="J44" s="3">
-        <v>681800</v>
+        <v>672400</v>
       </c>
       <c r="K44" s="3">
         <v>692600</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>422400</v>
+        <v>416600</v>
       </c>
       <c r="E45" s="3">
-        <v>537900</v>
+        <v>530500</v>
       </c>
       <c r="F45" s="3">
-        <v>579700</v>
+        <v>571700</v>
       </c>
       <c r="G45" s="3">
-        <v>668100</v>
+        <v>658900</v>
       </c>
       <c r="H45" s="3">
-        <v>428800</v>
+        <v>422800</v>
       </c>
       <c r="I45" s="3">
-        <v>363200</v>
+        <v>358200</v>
       </c>
       <c r="J45" s="3">
-        <v>356300</v>
+        <v>351300</v>
       </c>
       <c r="K45" s="3">
         <v>416200</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3646000</v>
+        <v>3595500</v>
       </c>
       <c r="E46" s="3">
-        <v>3213900</v>
+        <v>3169400</v>
       </c>
       <c r="F46" s="3">
-        <v>3521400</v>
+        <v>3472600</v>
       </c>
       <c r="G46" s="3">
-        <v>3647600</v>
+        <v>3597100</v>
       </c>
       <c r="H46" s="3">
-        <v>2407200</v>
+        <v>2373900</v>
       </c>
       <c r="I46" s="3">
-        <v>2294100</v>
+        <v>2262400</v>
       </c>
       <c r="J46" s="3">
-        <v>2115700</v>
+        <v>2086500</v>
       </c>
       <c r="K46" s="3">
         <v>2371900</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>28000</v>
+        <v>27600</v>
       </c>
       <c r="E47" s="3">
-        <v>20300</v>
+        <v>20000</v>
       </c>
       <c r="F47" s="3">
-        <v>112800</v>
+        <v>111300</v>
       </c>
       <c r="G47" s="3">
-        <v>115700</v>
+        <v>114100</v>
       </c>
       <c r="H47" s="3">
-        <v>130700</v>
+        <v>128900</v>
       </c>
       <c r="I47" s="3">
-        <v>87000</v>
+        <v>85800</v>
       </c>
       <c r="J47" s="3">
-        <v>82300</v>
+        <v>81100</v>
       </c>
       <c r="K47" s="3">
         <v>95800</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>644100</v>
+        <v>635200</v>
       </c>
       <c r="E48" s="3">
-        <v>668600</v>
+        <v>659300</v>
       </c>
       <c r="F48" s="3">
-        <v>693400</v>
+        <v>683800</v>
       </c>
       <c r="G48" s="3">
-        <v>768400</v>
+        <v>757800</v>
       </c>
       <c r="H48" s="3">
-        <v>293900</v>
+        <v>289800</v>
       </c>
       <c r="I48" s="3">
-        <v>286800</v>
+        <v>282800</v>
       </c>
       <c r="J48" s="3">
-        <v>293100</v>
+        <v>289000</v>
       </c>
       <c r="K48" s="3">
         <v>325200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7135700</v>
+        <v>7036900</v>
       </c>
       <c r="E49" s="3">
-        <v>6916200</v>
+        <v>6820500</v>
       </c>
       <c r="F49" s="3">
-        <v>6560100</v>
+        <v>6469200</v>
       </c>
       <c r="G49" s="3">
-        <v>6754900</v>
+        <v>6661400</v>
       </c>
       <c r="H49" s="3">
-        <v>6287900</v>
+        <v>6200900</v>
       </c>
       <c r="I49" s="3">
-        <v>5959400</v>
+        <v>5876900</v>
       </c>
       <c r="J49" s="3">
-        <v>5759300</v>
+        <v>5679600</v>
       </c>
       <c r="K49" s="3">
         <v>5666800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>221900</v>
+        <v>218800</v>
       </c>
       <c r="E52" s="3">
-        <v>395500</v>
+        <v>390000</v>
       </c>
       <c r="F52" s="3">
-        <v>212700</v>
+        <v>209800</v>
       </c>
       <c r="G52" s="3">
-        <v>204900</v>
+        <v>202000</v>
       </c>
       <c r="H52" s="3">
-        <v>207700</v>
+        <v>204800</v>
       </c>
       <c r="I52" s="3">
-        <v>180800</v>
+        <v>178300</v>
       </c>
       <c r="J52" s="3">
-        <v>171300</v>
+        <v>168900</v>
       </c>
       <c r="K52" s="3">
         <v>197600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11675700</v>
+        <v>11514000</v>
       </c>
       <c r="E54" s="3">
-        <v>11214500</v>
+        <v>11059200</v>
       </c>
       <c r="F54" s="3">
-        <v>11100400</v>
+        <v>10946700</v>
       </c>
       <c r="G54" s="3">
-        <v>11491600</v>
+        <v>11332500</v>
       </c>
       <c r="H54" s="3">
-        <v>9327300</v>
+        <v>9198200</v>
       </c>
       <c r="I54" s="3">
-        <v>8808100</v>
+        <v>8686100</v>
       </c>
       <c r="J54" s="3">
-        <v>8421700</v>
+        <v>8305100</v>
       </c>
       <c r="K54" s="3">
         <v>8657300</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>683300</v>
+        <v>673900</v>
       </c>
       <c r="E57" s="3">
-        <v>751100</v>
+        <v>740700</v>
       </c>
       <c r="F57" s="3">
-        <v>658700</v>
+        <v>649600</v>
       </c>
       <c r="G57" s="3">
-        <v>758200</v>
+        <v>747700</v>
       </c>
       <c r="H57" s="3">
-        <v>819500</v>
+        <v>808100</v>
       </c>
       <c r="I57" s="3">
-        <v>838600</v>
+        <v>827000</v>
       </c>
       <c r="J57" s="3">
-        <v>742200</v>
+        <v>731900</v>
       </c>
       <c r="K57" s="3">
         <v>820200</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1003400</v>
+        <v>989500</v>
       </c>
       <c r="E58" s="3">
-        <v>185800</v>
+        <v>183200</v>
       </c>
       <c r="F58" s="3">
-        <v>414200</v>
+        <v>408500</v>
       </c>
       <c r="G58" s="3">
-        <v>361700</v>
+        <v>356700</v>
       </c>
       <c r="H58" s="3">
-        <v>83900</v>
+        <v>82700</v>
       </c>
       <c r="I58" s="3">
-        <v>257600</v>
+        <v>254000</v>
       </c>
       <c r="J58" s="3">
-        <v>90500</v>
+        <v>89200</v>
       </c>
       <c r="K58" s="3">
         <v>142200</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1746500</v>
+        <v>1722300</v>
       </c>
       <c r="E59" s="3">
-        <v>1759900</v>
+        <v>1735600</v>
       </c>
       <c r="F59" s="3">
-        <v>1737800</v>
+        <v>1713700</v>
       </c>
       <c r="G59" s="3">
-        <v>1581700</v>
+        <v>1559800</v>
       </c>
       <c r="H59" s="3">
-        <v>1228000</v>
+        <v>1211000</v>
       </c>
       <c r="I59" s="3">
-        <v>1209200</v>
+        <v>1192500</v>
       </c>
       <c r="J59" s="3">
-        <v>1163700</v>
+        <v>1147600</v>
       </c>
       <c r="K59" s="3">
         <v>1094800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3433200</v>
+        <v>3385700</v>
       </c>
       <c r="E60" s="3">
-        <v>2696800</v>
+        <v>2659500</v>
       </c>
       <c r="F60" s="3">
-        <v>2810700</v>
+        <v>2771800</v>
       </c>
       <c r="G60" s="3">
-        <v>2701600</v>
+        <v>2664200</v>
       </c>
       <c r="H60" s="3">
-        <v>2131300</v>
+        <v>2101800</v>
       </c>
       <c r="I60" s="3">
-        <v>2305400</v>
+        <v>2273500</v>
       </c>
       <c r="J60" s="3">
-        <v>1996400</v>
+        <v>1968800</v>
       </c>
       <c r="K60" s="3">
         <v>2057200</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1762100</v>
+        <v>1737700</v>
       </c>
       <c r="E61" s="3">
-        <v>2752600</v>
+        <v>2714500</v>
       </c>
       <c r="F61" s="3">
-        <v>2673700</v>
+        <v>2636700</v>
       </c>
       <c r="G61" s="3">
-        <v>2936700</v>
+        <v>2896100</v>
       </c>
       <c r="H61" s="3">
-        <v>1638900</v>
+        <v>1616200</v>
       </c>
       <c r="I61" s="3">
-        <v>1073200</v>
+        <v>1058400</v>
       </c>
       <c r="J61" s="3">
-        <v>1285500</v>
+        <v>1267700</v>
       </c>
       <c r="K61" s="3">
         <v>1272600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>339200</v>
+        <v>334500</v>
       </c>
       <c r="E62" s="3">
-        <v>390600</v>
+        <v>385200</v>
       </c>
       <c r="F62" s="3">
-        <v>453200</v>
+        <v>446900</v>
       </c>
       <c r="G62" s="3">
-        <v>485100</v>
+        <v>478400</v>
       </c>
       <c r="H62" s="3">
-        <v>469900</v>
+        <v>463400</v>
       </c>
       <c r="I62" s="3">
-        <v>489400</v>
+        <v>482600</v>
       </c>
       <c r="J62" s="3">
-        <v>556100</v>
+        <v>548400</v>
       </c>
       <c r="K62" s="3">
         <v>541300</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5534400</v>
+        <v>5457800</v>
       </c>
       <c r="E66" s="3">
-        <v>5840000</v>
+        <v>5759200</v>
       </c>
       <c r="F66" s="3">
-        <v>5937600</v>
+        <v>5855400</v>
       </c>
       <c r="G66" s="3">
-        <v>6123400</v>
+        <v>6038600</v>
       </c>
       <c r="H66" s="3">
-        <v>4240100</v>
+        <v>4181400</v>
       </c>
       <c r="I66" s="3">
-        <v>3868100</v>
+        <v>3814500</v>
       </c>
       <c r="J66" s="3">
-        <v>3838000</v>
+        <v>3784900</v>
       </c>
       <c r="K66" s="3">
         <v>3871100</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4677100</v>
+        <v>4612400</v>
       </c>
       <c r="E72" s="3">
-        <v>4009000</v>
+        <v>3953500</v>
       </c>
       <c r="F72" s="3">
-        <v>3497100</v>
+        <v>3448700</v>
       </c>
       <c r="G72" s="3">
-        <v>3475900</v>
+        <v>3427800</v>
       </c>
       <c r="H72" s="3">
-        <v>3368200</v>
+        <v>3321600</v>
       </c>
       <c r="I72" s="3">
-        <v>3141800</v>
+        <v>3098300</v>
       </c>
       <c r="J72" s="3">
-        <v>2804100</v>
+        <v>2765200</v>
       </c>
       <c r="K72" s="3">
         <v>2797700</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6141200</v>
+        <v>6056200</v>
       </c>
       <c r="E76" s="3">
-        <v>5374500</v>
+        <v>5300100</v>
       </c>
       <c r="F76" s="3">
-        <v>5162800</v>
+        <v>5091300</v>
       </c>
       <c r="G76" s="3">
-        <v>5368100</v>
+        <v>5293800</v>
       </c>
       <c r="H76" s="3">
-        <v>5087300</v>
+        <v>5016900</v>
       </c>
       <c r="I76" s="3">
-        <v>4940000</v>
+        <v>4871600</v>
       </c>
       <c r="J76" s="3">
-        <v>4583700</v>
+        <v>4520200</v>
       </c>
       <c r="K76" s="3">
         <v>4786100</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1205500</v>
+        <v>1188800</v>
       </c>
       <c r="E81" s="3">
-        <v>1083500</v>
+        <v>1068500</v>
       </c>
       <c r="F81" s="3">
-        <v>1011700</v>
+        <v>997700</v>
       </c>
       <c r="G81" s="3">
-        <v>826100</v>
+        <v>814700</v>
       </c>
       <c r="H81" s="3">
-        <v>933500</v>
+        <v>920600</v>
       </c>
       <c r="I81" s="3">
-        <v>843500</v>
+        <v>831800</v>
       </c>
       <c r="J81" s="3">
-        <v>765000</v>
+        <v>754400</v>
       </c>
       <c r="K81" s="3">
         <v>791200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>375000</v>
+        <v>369800</v>
       </c>
       <c r="E83" s="3">
-        <v>344800</v>
+        <v>340000</v>
       </c>
       <c r="F83" s="3">
-        <v>372500</v>
+        <v>367300</v>
       </c>
       <c r="G83" s="3">
-        <v>418000</v>
+        <v>412300</v>
       </c>
       <c r="H83" s="3">
-        <v>289900</v>
+        <v>285900</v>
       </c>
       <c r="I83" s="3">
-        <v>290200</v>
+        <v>286200</v>
       </c>
       <c r="J83" s="3">
-        <v>278700</v>
+        <v>274900</v>
       </c>
       <c r="K83" s="3">
         <v>296200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1560900</v>
+        <v>1539300</v>
       </c>
       <c r="E89" s="3">
-        <v>1378200</v>
+        <v>1359100</v>
       </c>
       <c r="F89" s="3">
-        <v>1563600</v>
+        <v>1542000</v>
       </c>
       <c r="G89" s="3">
-        <v>1432600</v>
+        <v>1412700</v>
       </c>
       <c r="H89" s="3">
-        <v>1207400</v>
+        <v>1190700</v>
       </c>
       <c r="I89" s="3">
-        <v>1103600</v>
+        <v>1088300</v>
       </c>
       <c r="J89" s="3">
-        <v>1004000</v>
+        <v>990100</v>
       </c>
       <c r="K89" s="3">
         <v>987000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-116400</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-113800</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-88800</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-93600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-118100</v>
       </c>
-      <c r="E91" s="3">
-        <v>-115400</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-90000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-94900</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-119800</v>
-      </c>
       <c r="I91" s="3">
-        <v>-105900</v>
+        <v>-104400</v>
       </c>
       <c r="J91" s="3">
-        <v>-83300</v>
+        <v>-82100</v>
       </c>
       <c r="K91" s="3">
         <v>-122500</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-415200</v>
+        <v>-409500</v>
       </c>
       <c r="E94" s="3">
-        <v>-673900</v>
+        <v>-664600</v>
       </c>
       <c r="F94" s="3">
-        <v>-293800</v>
+        <v>-289700</v>
       </c>
       <c r="G94" s="3">
-        <v>-423000</v>
+        <v>-417200</v>
       </c>
       <c r="H94" s="3">
-        <v>-702600</v>
+        <v>-692900</v>
       </c>
       <c r="I94" s="3">
-        <v>-426700</v>
+        <v>-420800</v>
       </c>
       <c r="J94" s="3">
-        <v>-437700</v>
+        <v>-431600</v>
       </c>
       <c r="K94" s="3">
         <v>-283400</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-881200</v>
+        <v>-869000</v>
       </c>
       <c r="E100" s="3">
-        <v>-1175800</v>
+        <v>-1159500</v>
       </c>
       <c r="F100" s="3">
-        <v>-1221800</v>
+        <v>-1204800</v>
       </c>
       <c r="G100" s="3">
-        <v>69600</v>
+        <v>68600</v>
       </c>
       <c r="H100" s="3">
-        <v>-464900</v>
+        <v>-458500</v>
       </c>
       <c r="I100" s="3">
-        <v>-649600</v>
+        <v>-640600</v>
       </c>
       <c r="J100" s="3">
-        <v>-874200</v>
+        <v>-862100</v>
       </c>
       <c r="K100" s="3">
         <v>-493300</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>6600</v>
+        <v>6500</v>
       </c>
       <c r="E101" s="3">
-        <v>-34400</v>
+        <v>-33900</v>
       </c>
       <c r="F101" s="3">
-        <v>-54600</v>
+        <v>-53800</v>
       </c>
       <c r="G101" s="3">
-        <v>25000</v>
+        <v>24700</v>
       </c>
       <c r="H101" s="3">
-        <v>-17900</v>
+        <v>-17700</v>
       </c>
       <c r="I101" s="3">
-        <v>-13800</v>
+        <v>-13600</v>
       </c>
       <c r="J101" s="3">
-        <v>-10300</v>
+        <v>-10200</v>
       </c>
       <c r="K101" s="3">
         <v>5400</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>271100</v>
+        <v>267400</v>
       </c>
       <c r="E102" s="3">
-        <v>-505900</v>
+        <v>-498900</v>
       </c>
       <c r="F102" s="3">
-        <v>-6500</v>
+        <v>-6400</v>
       </c>
       <c r="G102" s="3">
-        <v>1104200</v>
+        <v>1088900</v>
       </c>
       <c r="H102" s="3">
-        <v>22000</v>
+        <v>21700</v>
       </c>
       <c r="I102" s="3">
-        <v>13500</v>
+        <v>13300</v>
       </c>
       <c r="J102" s="3">
-        <v>-318300</v>
+        <v>-313800</v>
       </c>
       <c r="K102" s="3">
         <v>215600</v>

--- a/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>10418600</v>
+        <v>10523700</v>
       </c>
       <c r="E8" s="3">
-        <v>9377100</v>
+        <v>9471700</v>
       </c>
       <c r="F8" s="3">
-        <v>8837500</v>
+        <v>8926700</v>
       </c>
       <c r="G8" s="3">
-        <v>8864700</v>
+        <v>8954100</v>
       </c>
       <c r="H8" s="3">
-        <v>8826200</v>
+        <v>8915200</v>
       </c>
       <c r="I8" s="3">
-        <v>8385700</v>
+        <v>8470300</v>
       </c>
       <c r="J8" s="3">
-        <v>7903500</v>
+        <v>7983200</v>
       </c>
       <c r="K8" s="3">
         <v>7909500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1086000</v>
+        <v>1097000</v>
       </c>
       <c r="E9" s="3">
-        <v>1034700</v>
+        <v>1045100</v>
       </c>
       <c r="F9" s="3">
-        <v>1079500</v>
+        <v>1090300</v>
       </c>
       <c r="G9" s="3">
-        <v>1123800</v>
+        <v>1135100</v>
       </c>
       <c r="H9" s="3">
-        <v>872300</v>
+        <v>881100</v>
       </c>
       <c r="I9" s="3">
-        <v>833100</v>
+        <v>841500</v>
       </c>
       <c r="J9" s="3">
-        <v>819200</v>
+        <v>827500</v>
       </c>
       <c r="K9" s="3">
         <v>840600</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9332600</v>
+        <v>9426700</v>
       </c>
       <c r="E10" s="3">
-        <v>8342400</v>
+        <v>8426600</v>
       </c>
       <c r="F10" s="3">
-        <v>7758100</v>
+        <v>7836300</v>
       </c>
       <c r="G10" s="3">
-        <v>7741000</v>
+        <v>7819000</v>
       </c>
       <c r="H10" s="3">
-        <v>7953900</v>
+        <v>8034100</v>
       </c>
       <c r="I10" s="3">
-        <v>7552600</v>
+        <v>7628800</v>
       </c>
       <c r="J10" s="3">
-        <v>7084200</v>
+        <v>7155700</v>
       </c>
       <c r="K10" s="3">
         <v>7068900</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>45800</v>
+        <v>46300</v>
       </c>
       <c r="E14" s="3">
-        <v>23700</v>
+        <v>23900</v>
       </c>
       <c r="F14" s="3">
-        <v>12400</v>
+        <v>12500</v>
       </c>
       <c r="G14" s="3">
-        <v>182300</v>
+        <v>184100</v>
       </c>
       <c r="H14" s="3">
-        <v>56400</v>
+        <v>57000</v>
       </c>
       <c r="I14" s="3">
-        <v>100500</v>
+        <v>101500</v>
       </c>
       <c r="J14" s="3">
-        <v>72100</v>
+        <v>72800</v>
       </c>
       <c r="K14" s="3">
         <v>21500</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>41500</v>
+        <v>41900</v>
       </c>
       <c r="E15" s="3">
-        <v>35400</v>
+        <v>35800</v>
       </c>
       <c r="F15" s="3">
-        <v>44700</v>
+        <v>45200</v>
       </c>
       <c r="G15" s="3">
-        <v>40700</v>
+        <v>41200</v>
       </c>
       <c r="H15" s="3">
-        <v>46800</v>
+        <v>47300</v>
       </c>
       <c r="I15" s="3">
-        <v>51200</v>
+        <v>51800</v>
       </c>
       <c r="J15" s="3">
-        <v>41200</v>
+        <v>41600</v>
       </c>
       <c r="K15" s="3">
         <v>40000</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8816900</v>
+        <v>8905800</v>
       </c>
       <c r="E17" s="3">
-        <v>7943700</v>
+        <v>8023800</v>
       </c>
       <c r="F17" s="3">
-        <v>7498100</v>
+        <v>7573700</v>
       </c>
       <c r="G17" s="3">
-        <v>7759700</v>
+        <v>7838000</v>
       </c>
       <c r="H17" s="3">
-        <v>7604100</v>
+        <v>7680800</v>
       </c>
       <c r="I17" s="3">
-        <v>7299900</v>
+        <v>7373500</v>
       </c>
       <c r="J17" s="3">
-        <v>6870100</v>
+        <v>6939400</v>
       </c>
       <c r="K17" s="3">
         <v>6833900</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1601800</v>
+        <v>1617900</v>
       </c>
       <c r="E18" s="3">
-        <v>1433400</v>
+        <v>1447900</v>
       </c>
       <c r="F18" s="3">
-        <v>1339500</v>
+        <v>1353000</v>
       </c>
       <c r="G18" s="3">
-        <v>1105000</v>
+        <v>1116100</v>
       </c>
       <c r="H18" s="3">
-        <v>1222100</v>
+        <v>1234400</v>
       </c>
       <c r="I18" s="3">
-        <v>1085800</v>
+        <v>1096800</v>
       </c>
       <c r="J18" s="3">
-        <v>1033300</v>
+        <v>1043700</v>
       </c>
       <c r="K18" s="3">
         <v>1075600</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1970600</v>
+        <v>1991600</v>
       </c>
       <c r="E21" s="3">
-        <v>1772600</v>
+        <v>1791500</v>
       </c>
       <c r="F21" s="3">
-        <v>1705800</v>
+        <v>1724100</v>
       </c>
       <c r="G21" s="3">
-        <v>1516200</v>
+        <v>1532700</v>
       </c>
       <c r="H21" s="3">
-        <v>1507300</v>
+        <v>1523300</v>
       </c>
       <c r="I21" s="3">
-        <v>1371300</v>
+        <v>1385900</v>
       </c>
       <c r="J21" s="3">
-        <v>1307500</v>
+        <v>1321500</v>
       </c>
       <c r="K21" s="3">
         <v>1371800</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1601800</v>
+        <v>1617900</v>
       </c>
       <c r="E23" s="3">
-        <v>1433400</v>
+        <v>1447900</v>
       </c>
       <c r="F23" s="3">
-        <v>1339500</v>
+        <v>1353000</v>
       </c>
       <c r="G23" s="3">
-        <v>1105000</v>
+        <v>1116100</v>
       </c>
       <c r="H23" s="3">
-        <v>1222100</v>
+        <v>1234400</v>
       </c>
       <c r="I23" s="3">
-        <v>1085800</v>
+        <v>1096800</v>
       </c>
       <c r="J23" s="3">
-        <v>1033300</v>
+        <v>1043700</v>
       </c>
       <c r="K23" s="3">
         <v>1075600</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>413000</v>
+        <v>417100</v>
       </c>
       <c r="E24" s="3">
-        <v>365000</v>
+        <v>368700</v>
       </c>
       <c r="F24" s="3">
-        <v>341700</v>
+        <v>345200</v>
       </c>
       <c r="G24" s="3">
-        <v>290300</v>
+        <v>293300</v>
       </c>
       <c r="H24" s="3">
-        <v>301500</v>
+        <v>304600</v>
       </c>
       <c r="I24" s="3">
-        <v>254000</v>
+        <v>256600</v>
       </c>
       <c r="J24" s="3">
-        <v>278900</v>
+        <v>281700</v>
       </c>
       <c r="K24" s="3">
         <v>284300</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1188800</v>
+        <v>1200800</v>
       </c>
       <c r="E26" s="3">
-        <v>1068500</v>
+        <v>1079200</v>
       </c>
       <c r="F26" s="3">
-        <v>997700</v>
+        <v>1007800</v>
       </c>
       <c r="G26" s="3">
-        <v>814700</v>
+        <v>822900</v>
       </c>
       <c r="H26" s="3">
-        <v>920600</v>
+        <v>929900</v>
       </c>
       <c r="I26" s="3">
-        <v>831800</v>
+        <v>840200</v>
       </c>
       <c r="J26" s="3">
-        <v>754400</v>
+        <v>762000</v>
       </c>
       <c r="K26" s="3">
         <v>791200</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1188800</v>
+        <v>1200800</v>
       </c>
       <c r="E27" s="3">
-        <v>1068500</v>
+        <v>1079200</v>
       </c>
       <c r="F27" s="3">
-        <v>997700</v>
+        <v>1007800</v>
       </c>
       <c r="G27" s="3">
-        <v>814700</v>
+        <v>822900</v>
       </c>
       <c r="H27" s="3">
-        <v>920600</v>
+        <v>929900</v>
       </c>
       <c r="I27" s="3">
-        <v>831800</v>
+        <v>840200</v>
       </c>
       <c r="J27" s="3">
-        <v>754400</v>
+        <v>762000</v>
       </c>
       <c r="K27" s="3">
         <v>791200</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1188800</v>
+        <v>1200800</v>
       </c>
       <c r="E33" s="3">
-        <v>1068500</v>
+        <v>1079200</v>
       </c>
       <c r="F33" s="3">
-        <v>997700</v>
+        <v>1007800</v>
       </c>
       <c r="G33" s="3">
-        <v>814700</v>
+        <v>822900</v>
       </c>
       <c r="H33" s="3">
-        <v>920600</v>
+        <v>929900</v>
       </c>
       <c r="I33" s="3">
-        <v>831800</v>
+        <v>840200</v>
       </c>
       <c r="J33" s="3">
-        <v>754400</v>
+        <v>762000</v>
       </c>
       <c r="K33" s="3">
         <v>791200</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1188800</v>
+        <v>1200800</v>
       </c>
       <c r="E35" s="3">
-        <v>1068500</v>
+        <v>1079200</v>
       </c>
       <c r="F35" s="3">
-        <v>997700</v>
+        <v>1007800</v>
       </c>
       <c r="G35" s="3">
-        <v>814700</v>
+        <v>822900</v>
       </c>
       <c r="H35" s="3">
-        <v>920600</v>
+        <v>929900</v>
       </c>
       <c r="I35" s="3">
-        <v>831800</v>
+        <v>840200</v>
       </c>
       <c r="J35" s="3">
-        <v>754400</v>
+        <v>762000</v>
       </c>
       <c r="K35" s="3">
         <v>791200</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1142900</v>
+        <v>1154400</v>
       </c>
       <c r="E41" s="3">
-        <v>704300</v>
+        <v>711400</v>
       </c>
       <c r="F41" s="3">
-        <v>1238300</v>
+        <v>1250800</v>
       </c>
       <c r="G41" s="3">
-        <v>1244700</v>
+        <v>1257300</v>
       </c>
       <c r="H41" s="3">
-        <v>155800</v>
+        <v>157400</v>
       </c>
       <c r="I41" s="3">
-        <v>134200</v>
+        <v>135500</v>
       </c>
       <c r="J41" s="3">
-        <v>120900</v>
+        <v>122100</v>
       </c>
       <c r="K41" s="3">
         <v>441600</v>
@@ -2038,7 +2038,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>58300</v>
+        <v>58900</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>8</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1144200</v>
+        <v>1155800</v>
       </c>
       <c r="E43" s="3">
-        <v>1066000</v>
+        <v>1076800</v>
       </c>
       <c r="F43" s="3">
-        <v>901000</v>
+        <v>910100</v>
       </c>
       <c r="G43" s="3">
-        <v>910000</v>
+        <v>919200</v>
       </c>
       <c r="H43" s="3">
-        <v>996400</v>
+        <v>1006500</v>
       </c>
       <c r="I43" s="3">
-        <v>1082900</v>
+        <v>1093900</v>
       </c>
       <c r="J43" s="3">
-        <v>941900</v>
+        <v>951400</v>
       </c>
       <c r="K43" s="3">
         <v>821400</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>833500</v>
+        <v>841900</v>
       </c>
       <c r="E44" s="3">
-        <v>868600</v>
+        <v>877300</v>
       </c>
       <c r="F44" s="3">
-        <v>761600</v>
+        <v>769300</v>
       </c>
       <c r="G44" s="3">
-        <v>783600</v>
+        <v>791500</v>
       </c>
       <c r="H44" s="3">
-        <v>798700</v>
+        <v>806800</v>
       </c>
       <c r="I44" s="3">
-        <v>687100</v>
+        <v>694000</v>
       </c>
       <c r="J44" s="3">
-        <v>672400</v>
+        <v>679100</v>
       </c>
       <c r="K44" s="3">
         <v>692600</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>416600</v>
+        <v>420800</v>
       </c>
       <c r="E45" s="3">
-        <v>530500</v>
+        <v>535900</v>
       </c>
       <c r="F45" s="3">
-        <v>571700</v>
+        <v>577500</v>
       </c>
       <c r="G45" s="3">
-        <v>658900</v>
+        <v>665500</v>
       </c>
       <c r="H45" s="3">
-        <v>422800</v>
+        <v>427100</v>
       </c>
       <c r="I45" s="3">
-        <v>358200</v>
+        <v>361800</v>
       </c>
       <c r="J45" s="3">
-        <v>351300</v>
+        <v>354900</v>
       </c>
       <c r="K45" s="3">
         <v>416200</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3595500</v>
+        <v>3631800</v>
       </c>
       <c r="E46" s="3">
-        <v>3169400</v>
+        <v>3201400</v>
       </c>
       <c r="F46" s="3">
-        <v>3472600</v>
+        <v>3507700</v>
       </c>
       <c r="G46" s="3">
-        <v>3597100</v>
+        <v>3633400</v>
       </c>
       <c r="H46" s="3">
-        <v>2373900</v>
+        <v>2397800</v>
       </c>
       <c r="I46" s="3">
-        <v>2262400</v>
+        <v>2285200</v>
       </c>
       <c r="J46" s="3">
-        <v>2086500</v>
+        <v>2107500</v>
       </c>
       <c r="K46" s="3">
         <v>2371900</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>27600</v>
+        <v>27900</v>
       </c>
       <c r="E47" s="3">
-        <v>20000</v>
+        <v>20200</v>
       </c>
       <c r="F47" s="3">
-        <v>111300</v>
+        <v>112400</v>
       </c>
       <c r="G47" s="3">
-        <v>114100</v>
+        <v>115300</v>
       </c>
       <c r="H47" s="3">
-        <v>128900</v>
+        <v>130200</v>
       </c>
       <c r="I47" s="3">
-        <v>85800</v>
+        <v>86700</v>
       </c>
       <c r="J47" s="3">
-        <v>81100</v>
+        <v>81900</v>
       </c>
       <c r="K47" s="3">
         <v>95800</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>635200</v>
+        <v>641600</v>
       </c>
       <c r="E48" s="3">
-        <v>659300</v>
+        <v>666000</v>
       </c>
       <c r="F48" s="3">
-        <v>683800</v>
+        <v>690700</v>
       </c>
       <c r="G48" s="3">
-        <v>757800</v>
+        <v>765400</v>
       </c>
       <c r="H48" s="3">
-        <v>289800</v>
+        <v>292700</v>
       </c>
       <c r="I48" s="3">
-        <v>282800</v>
+        <v>285700</v>
       </c>
       <c r="J48" s="3">
-        <v>289000</v>
+        <v>292000</v>
       </c>
       <c r="K48" s="3">
         <v>325200</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7036900</v>
+        <v>7107900</v>
       </c>
       <c r="E49" s="3">
-        <v>6820500</v>
+        <v>6889300</v>
       </c>
       <c r="F49" s="3">
-        <v>6469200</v>
+        <v>6534500</v>
       </c>
       <c r="G49" s="3">
-        <v>6661400</v>
+        <v>6728600</v>
       </c>
       <c r="H49" s="3">
-        <v>6200900</v>
+        <v>6263400</v>
       </c>
       <c r="I49" s="3">
-        <v>5876900</v>
+        <v>5936100</v>
       </c>
       <c r="J49" s="3">
-        <v>5679600</v>
+        <v>5736900</v>
       </c>
       <c r="K49" s="3">
         <v>5666800</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>218800</v>
+        <v>221000</v>
       </c>
       <c r="E52" s="3">
-        <v>390000</v>
+        <v>394000</v>
       </c>
       <c r="F52" s="3">
-        <v>209800</v>
+        <v>211900</v>
       </c>
       <c r="G52" s="3">
-        <v>202000</v>
+        <v>204100</v>
       </c>
       <c r="H52" s="3">
-        <v>204800</v>
+        <v>206900</v>
       </c>
       <c r="I52" s="3">
-        <v>178300</v>
+        <v>180100</v>
       </c>
       <c r="J52" s="3">
-        <v>168900</v>
+        <v>170600</v>
       </c>
       <c r="K52" s="3">
         <v>197600</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11514000</v>
+        <v>11630200</v>
       </c>
       <c r="E54" s="3">
-        <v>11059200</v>
+        <v>11170800</v>
       </c>
       <c r="F54" s="3">
-        <v>10946700</v>
+        <v>11057100</v>
       </c>
       <c r="G54" s="3">
-        <v>11332500</v>
+        <v>11446800</v>
       </c>
       <c r="H54" s="3">
-        <v>9198200</v>
+        <v>9291000</v>
       </c>
       <c r="I54" s="3">
-        <v>8686100</v>
+        <v>8773700</v>
       </c>
       <c r="J54" s="3">
-        <v>8305100</v>
+        <v>8388900</v>
       </c>
       <c r="K54" s="3">
         <v>8657300</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>673900</v>
+        <v>680700</v>
       </c>
       <c r="E57" s="3">
-        <v>740700</v>
+        <v>748200</v>
       </c>
       <c r="F57" s="3">
-        <v>649600</v>
+        <v>656100</v>
       </c>
       <c r="G57" s="3">
-        <v>747700</v>
+        <v>755200</v>
       </c>
       <c r="H57" s="3">
-        <v>808100</v>
+        <v>816300</v>
       </c>
       <c r="I57" s="3">
-        <v>827000</v>
+        <v>835300</v>
       </c>
       <c r="J57" s="3">
-        <v>731900</v>
+        <v>739300</v>
       </c>
       <c r="K57" s="3">
         <v>820200</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>989500</v>
+        <v>999500</v>
       </c>
       <c r="E58" s="3">
-        <v>183200</v>
+        <v>185100</v>
       </c>
       <c r="F58" s="3">
-        <v>408500</v>
+        <v>412600</v>
       </c>
       <c r="G58" s="3">
-        <v>356700</v>
+        <v>360300</v>
       </c>
       <c r="H58" s="3">
-        <v>82700</v>
+        <v>83600</v>
       </c>
       <c r="I58" s="3">
-        <v>254000</v>
+        <v>256600</v>
       </c>
       <c r="J58" s="3">
-        <v>89200</v>
+        <v>90100</v>
       </c>
       <c r="K58" s="3">
         <v>142200</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1722300</v>
+        <v>1739700</v>
       </c>
       <c r="E59" s="3">
-        <v>1735600</v>
+        <v>1753100</v>
       </c>
       <c r="F59" s="3">
-        <v>1713700</v>
+        <v>1731000</v>
       </c>
       <c r="G59" s="3">
-        <v>1559800</v>
+        <v>1575600</v>
       </c>
       <c r="H59" s="3">
-        <v>1211000</v>
+        <v>1223200</v>
       </c>
       <c r="I59" s="3">
-        <v>1192500</v>
+        <v>1204500</v>
       </c>
       <c r="J59" s="3">
-        <v>1147600</v>
+        <v>1159200</v>
       </c>
       <c r="K59" s="3">
         <v>1094800</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3385700</v>
+        <v>3419800</v>
       </c>
       <c r="E60" s="3">
-        <v>2659500</v>
+        <v>2686300</v>
       </c>
       <c r="F60" s="3">
-        <v>2771800</v>
+        <v>2799800</v>
       </c>
       <c r="G60" s="3">
-        <v>2664200</v>
+        <v>2691100</v>
       </c>
       <c r="H60" s="3">
-        <v>2101800</v>
+        <v>2123000</v>
       </c>
       <c r="I60" s="3">
-        <v>2273500</v>
+        <v>2296400</v>
       </c>
       <c r="J60" s="3">
-        <v>1968800</v>
+        <v>1988600</v>
       </c>
       <c r="K60" s="3">
         <v>2057200</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1737700</v>
+        <v>1755200</v>
       </c>
       <c r="E61" s="3">
-        <v>2714500</v>
+        <v>2741900</v>
       </c>
       <c r="F61" s="3">
-        <v>2636700</v>
+        <v>2663300</v>
       </c>
       <c r="G61" s="3">
-        <v>2896100</v>
+        <v>2925300</v>
       </c>
       <c r="H61" s="3">
-        <v>1616200</v>
+        <v>1632500</v>
       </c>
       <c r="I61" s="3">
-        <v>1058400</v>
+        <v>1069100</v>
       </c>
       <c r="J61" s="3">
-        <v>1267700</v>
+        <v>1280500</v>
       </c>
       <c r="K61" s="3">
         <v>1272600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>334500</v>
+        <v>337800</v>
       </c>
       <c r="E62" s="3">
-        <v>385200</v>
+        <v>389000</v>
       </c>
       <c r="F62" s="3">
-        <v>446900</v>
+        <v>451400</v>
       </c>
       <c r="G62" s="3">
-        <v>478400</v>
+        <v>483200</v>
       </c>
       <c r="H62" s="3">
-        <v>463400</v>
+        <v>468000</v>
       </c>
       <c r="I62" s="3">
-        <v>482600</v>
+        <v>487500</v>
       </c>
       <c r="J62" s="3">
-        <v>548400</v>
+        <v>553900</v>
       </c>
       <c r="K62" s="3">
         <v>541300</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5457800</v>
+        <v>5512900</v>
       </c>
       <c r="E66" s="3">
-        <v>5759200</v>
+        <v>5817300</v>
       </c>
       <c r="F66" s="3">
-        <v>5855400</v>
+        <v>5914500</v>
       </c>
       <c r="G66" s="3">
-        <v>6038600</v>
+        <v>6099600</v>
       </c>
       <c r="H66" s="3">
-        <v>4181400</v>
+        <v>4223500</v>
       </c>
       <c r="I66" s="3">
-        <v>3814500</v>
+        <v>3853000</v>
       </c>
       <c r="J66" s="3">
-        <v>3784900</v>
+        <v>3823100</v>
       </c>
       <c r="K66" s="3">
         <v>3871100</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4612400</v>
+        <v>4658900</v>
       </c>
       <c r="E72" s="3">
-        <v>3953500</v>
+        <v>3993400</v>
       </c>
       <c r="F72" s="3">
-        <v>3448700</v>
+        <v>3483400</v>
       </c>
       <c r="G72" s="3">
-        <v>3427800</v>
+        <v>3462400</v>
       </c>
       <c r="H72" s="3">
-        <v>3321600</v>
+        <v>3355100</v>
       </c>
       <c r="I72" s="3">
-        <v>3098300</v>
+        <v>3129500</v>
       </c>
       <c r="J72" s="3">
-        <v>2765200</v>
+        <v>2793100</v>
       </c>
       <c r="K72" s="3">
         <v>2797700</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6056200</v>
+        <v>6117300</v>
       </c>
       <c r="E76" s="3">
-        <v>5300100</v>
+        <v>5353500</v>
       </c>
       <c r="F76" s="3">
-        <v>5091300</v>
+        <v>5142600</v>
       </c>
       <c r="G76" s="3">
-        <v>5293800</v>
+        <v>5347200</v>
       </c>
       <c r="H76" s="3">
-        <v>5016900</v>
+        <v>5067500</v>
       </c>
       <c r="I76" s="3">
-        <v>4871600</v>
+        <v>4920800</v>
       </c>
       <c r="J76" s="3">
-        <v>4520200</v>
+        <v>4565800</v>
       </c>
       <c r="K76" s="3">
         <v>4786100</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1188800</v>
+        <v>1200800</v>
       </c>
       <c r="E81" s="3">
-        <v>1068500</v>
+        <v>1079200</v>
       </c>
       <c r="F81" s="3">
-        <v>997700</v>
+        <v>1007800</v>
       </c>
       <c r="G81" s="3">
-        <v>814700</v>
+        <v>822900</v>
       </c>
       <c r="H81" s="3">
-        <v>920600</v>
+        <v>929900</v>
       </c>
       <c r="I81" s="3">
-        <v>831800</v>
+        <v>840200</v>
       </c>
       <c r="J81" s="3">
-        <v>754400</v>
+        <v>762000</v>
       </c>
       <c r="K81" s="3">
         <v>791200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>369800</v>
+        <v>373500</v>
       </c>
       <c r="E83" s="3">
-        <v>340000</v>
+        <v>343400</v>
       </c>
       <c r="F83" s="3">
-        <v>367300</v>
+        <v>371000</v>
       </c>
       <c r="G83" s="3">
-        <v>412300</v>
+        <v>416400</v>
       </c>
       <c r="H83" s="3">
-        <v>285900</v>
+        <v>288800</v>
       </c>
       <c r="I83" s="3">
-        <v>286200</v>
+        <v>289100</v>
       </c>
       <c r="J83" s="3">
-        <v>274900</v>
+        <v>277700</v>
       </c>
       <c r="K83" s="3">
         <v>296200</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1539300</v>
+        <v>1554800</v>
       </c>
       <c r="E89" s="3">
-        <v>1359100</v>
+        <v>1372800</v>
       </c>
       <c r="F89" s="3">
-        <v>1542000</v>
+        <v>1557600</v>
       </c>
       <c r="G89" s="3">
-        <v>1412700</v>
+        <v>1427000</v>
       </c>
       <c r="H89" s="3">
-        <v>1190700</v>
+        <v>1202700</v>
       </c>
       <c r="I89" s="3">
-        <v>1088300</v>
+        <v>1099300</v>
       </c>
       <c r="J89" s="3">
-        <v>990100</v>
+        <v>1000000</v>
       </c>
       <c r="K89" s="3">
         <v>987000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-116400</v>
+        <v>-117600</v>
       </c>
       <c r="E91" s="3">
-        <v>-113800</v>
+        <v>-114900</v>
       </c>
       <c r="F91" s="3">
-        <v>-88800</v>
+        <v>-89700</v>
       </c>
       <c r="G91" s="3">
-        <v>-93600</v>
+        <v>-94600</v>
       </c>
       <c r="H91" s="3">
-        <v>-118100</v>
+        <v>-119300</v>
       </c>
       <c r="I91" s="3">
-        <v>-104400</v>
+        <v>-105400</v>
       </c>
       <c r="J91" s="3">
-        <v>-82100</v>
+        <v>-82900</v>
       </c>
       <c r="K91" s="3">
         <v>-122500</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-409500</v>
+        <v>-413600</v>
       </c>
       <c r="E94" s="3">
-        <v>-664600</v>
+        <v>-671300</v>
       </c>
       <c r="F94" s="3">
-        <v>-289700</v>
+        <v>-292600</v>
       </c>
       <c r="G94" s="3">
-        <v>-417200</v>
+        <v>-421400</v>
       </c>
       <c r="H94" s="3">
-        <v>-692900</v>
+        <v>-699900</v>
       </c>
       <c r="I94" s="3">
-        <v>-420800</v>
+        <v>-425000</v>
       </c>
       <c r="J94" s="3">
-        <v>-431600</v>
+        <v>-436000</v>
       </c>
       <c r="K94" s="3">
         <v>-283400</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-869000</v>
+        <v>-877700</v>
       </c>
       <c r="E100" s="3">
-        <v>-1159500</v>
+        <v>-1171200</v>
       </c>
       <c r="F100" s="3">
-        <v>-1204800</v>
+        <v>-1217000</v>
       </c>
       <c r="G100" s="3">
-        <v>68600</v>
+        <v>69300</v>
       </c>
       <c r="H100" s="3">
-        <v>-458500</v>
+        <v>-463100</v>
       </c>
       <c r="I100" s="3">
-        <v>-640600</v>
+        <v>-647100</v>
       </c>
       <c r="J100" s="3">
-        <v>-862100</v>
+        <v>-870800</v>
       </c>
       <c r="K100" s="3">
         <v>-493300</v>
@@ -4455,22 +4455,22 @@
         <v>6500</v>
       </c>
       <c r="E101" s="3">
-        <v>-33900</v>
+        <v>-34200</v>
       </c>
       <c r="F101" s="3">
-        <v>-53800</v>
+        <v>-54400</v>
       </c>
       <c r="G101" s="3">
-        <v>24700</v>
+        <v>24900</v>
       </c>
       <c r="H101" s="3">
-        <v>-17700</v>
+        <v>-17900</v>
       </c>
       <c r="I101" s="3">
-        <v>-13600</v>
+        <v>-13800</v>
       </c>
       <c r="J101" s="3">
-        <v>-10200</v>
+        <v>-10300</v>
       </c>
       <c r="K101" s="3">
         <v>5400</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>267400</v>
+        <v>270100</v>
       </c>
       <c r="E102" s="3">
-        <v>-498900</v>
+        <v>-503900</v>
       </c>
       <c r="F102" s="3">
-        <v>-6400</v>
+        <v>-6500</v>
       </c>
       <c r="G102" s="3">
-        <v>1088900</v>
+        <v>1099900</v>
       </c>
       <c r="H102" s="3">
-        <v>21700</v>
+        <v>21900</v>
       </c>
       <c r="I102" s="3">
-        <v>13300</v>
+        <v>13400</v>
       </c>
       <c r="J102" s="3">
-        <v>-313800</v>
+        <v>-317000</v>
       </c>
       <c r="K102" s="3">
         <v>215600</v>

--- a/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>GIB</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44469</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44104</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43738</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43373</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43008</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42643</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42277</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41912</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41547</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41182</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40816</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>10523700</v>
+        <v>10863600</v>
       </c>
       <c r="E8" s="3">
-        <v>9471700</v>
+        <v>10568400</v>
       </c>
       <c r="F8" s="3">
-        <v>8926700</v>
+        <v>9371900</v>
       </c>
       <c r="G8" s="3">
-        <v>8954100</v>
+        <v>9591100</v>
       </c>
       <c r="H8" s="3">
-        <v>8915200</v>
+        <v>9129800</v>
       </c>
       <c r="I8" s="3">
-        <v>8470300</v>
+        <v>9148600</v>
       </c>
       <c r="J8" s="3">
+        <v>8901700</v>
+      </c>
+      <c r="K8" s="3">
         <v>7983200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7909500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7959600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8186300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7675300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3551700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3245000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1097000</v>
+        <v>7574200</v>
       </c>
       <c r="E9" s="3">
-        <v>1045100</v>
+        <v>7330700</v>
       </c>
       <c r="F9" s="3">
-        <v>1090300</v>
+        <v>6413100</v>
       </c>
       <c r="G9" s="3">
-        <v>1135100</v>
+        <v>6616900</v>
       </c>
       <c r="H9" s="3">
-        <v>881100</v>
+        <v>6249500</v>
       </c>
       <c r="I9" s="3">
-        <v>841500</v>
+        <v>6344700</v>
       </c>
       <c r="J9" s="3">
+        <v>6180700</v>
+      </c>
+      <c r="K9" s="3">
         <v>827500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>840600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>867300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>952900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>975400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3145700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2835500</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9426700</v>
+        <v>3289300</v>
       </c>
       <c r="E10" s="3">
-        <v>8426600</v>
+        <v>3237700</v>
       </c>
       <c r="F10" s="3">
-        <v>7836300</v>
+        <v>2958800</v>
       </c>
       <c r="G10" s="3">
-        <v>7819000</v>
+        <v>2974200</v>
       </c>
       <c r="H10" s="3">
-        <v>8034100</v>
+        <v>2880300</v>
       </c>
       <c r="I10" s="3">
-        <v>7628800</v>
+        <v>2803900</v>
       </c>
       <c r="J10" s="3">
+        <v>2721000</v>
+      </c>
+      <c r="K10" s="3">
         <v>7155700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7068900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7092300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7233400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6699900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>406000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>409500</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,31 +886,32 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F12" s="3">
+        <v>10700</v>
+      </c>
+      <c r="G12" s="3">
+        <v>11000</v>
+      </c>
+      <c r="H12" s="3">
+        <v>9700</v>
+      </c>
+      <c r="I12" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J12" s="3">
+        <v>6900</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>46300</v>
+        <v>80400</v>
       </c>
       <c r="E14" s="3">
-        <v>23900</v>
+        <v>47800</v>
       </c>
       <c r="F14" s="3">
-        <v>12500</v>
+        <v>23700</v>
       </c>
       <c r="G14" s="3">
-        <v>184100</v>
+        <v>9800</v>
       </c>
       <c r="H14" s="3">
-        <v>57000</v>
+        <v>184700</v>
       </c>
       <c r="I14" s="3">
-        <v>101500</v>
+        <v>58500</v>
       </c>
       <c r="J14" s="3">
+        <v>106700</v>
+      </c>
+      <c r="K14" s="3">
         <v>72800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>21500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>31900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>99300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>257600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>189800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2800</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>41900</v>
+        <v>378000</v>
       </c>
       <c r="E15" s="3">
-        <v>35800</v>
+        <v>372500</v>
       </c>
       <c r="F15" s="3">
-        <v>45200</v>
+        <v>337600</v>
       </c>
       <c r="G15" s="3">
-        <v>41200</v>
+        <v>395800</v>
       </c>
       <c r="H15" s="3">
-        <v>47300</v>
+        <v>406900</v>
       </c>
       <c r="I15" s="3">
-        <v>51800</v>
+        <v>293200</v>
       </c>
       <c r="J15" s="3">
+        <v>296900</v>
+      </c>
+      <c r="K15" s="3">
         <v>41600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>40000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>60400</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8905800</v>
+        <v>9071800</v>
       </c>
       <c r="E17" s="3">
-        <v>8023800</v>
+        <v>8859700</v>
       </c>
       <c r="F17" s="3">
-        <v>7573700</v>
+        <v>7846900</v>
       </c>
       <c r="G17" s="3">
-        <v>7838000</v>
+        <v>8047800</v>
       </c>
       <c r="H17" s="3">
-        <v>7680800</v>
+        <v>7723200</v>
       </c>
       <c r="I17" s="3">
-        <v>7373500</v>
+        <v>7771200</v>
       </c>
       <c r="J17" s="3">
+        <v>7587100</v>
+      </c>
+      <c r="K17" s="3">
         <v>6939400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6833900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6931700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7305100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7197600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3356000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2831800</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1617900</v>
+        <v>1791700</v>
       </c>
       <c r="E18" s="3">
-        <v>1447900</v>
+        <v>1708700</v>
       </c>
       <c r="F18" s="3">
-        <v>1353000</v>
+        <v>1525100</v>
       </c>
       <c r="G18" s="3">
-        <v>1116100</v>
+        <v>1543300</v>
       </c>
       <c r="H18" s="3">
-        <v>1234400</v>
+        <v>1406600</v>
       </c>
       <c r="I18" s="3">
-        <v>1096800</v>
+        <v>1377400</v>
       </c>
       <c r="J18" s="3">
+        <v>1314600</v>
+      </c>
+      <c r="K18" s="3">
         <v>1043700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1075600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1028000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>881200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>477700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>195700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>413200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,31 +1211,32 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-41600</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-25200</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>13100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>8900</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1223,77 +1256,83 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1991600</v>
+        <v>2211400</v>
       </c>
       <c r="E21" s="3">
-        <v>1791500</v>
+        <v>2106400</v>
       </c>
       <c r="F21" s="3">
-        <v>1724100</v>
+        <v>1853600</v>
       </c>
       <c r="G21" s="3">
-        <v>1532700</v>
+        <v>1936600</v>
       </c>
       <c r="H21" s="3">
-        <v>1523300</v>
+        <v>1807400</v>
       </c>
       <c r="I21" s="3">
-        <v>1385900</v>
+        <v>1657400</v>
       </c>
       <c r="J21" s="3">
+        <v>1602600</v>
+      </c>
+      <c r="K21" s="3">
         <v>1321500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1371800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1355000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1232300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>808700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>368200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>585600</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>57200</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>61300</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>62000</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>79700</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>81600</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>47800</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>48600</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1313,99 +1352,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1617900</v>
+        <v>1695800</v>
       </c>
       <c r="E23" s="3">
-        <v>1447900</v>
+        <v>1624800</v>
       </c>
       <c r="F23" s="3">
-        <v>1353000</v>
+        <v>1432700</v>
       </c>
       <c r="G23" s="3">
-        <v>1116100</v>
+        <v>1453700</v>
       </c>
       <c r="H23" s="3">
-        <v>1234400</v>
+        <v>1138000</v>
       </c>
       <c r="I23" s="3">
-        <v>1096800</v>
+        <v>1266700</v>
       </c>
       <c r="J23" s="3">
+        <v>1152600</v>
+      </c>
+      <c r="K23" s="3">
         <v>1043700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1075600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1028000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>881200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>477700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>195700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>413200</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>417100</v>
+        <v>442800</v>
       </c>
       <c r="E24" s="3">
-        <v>368700</v>
+        <v>418900</v>
       </c>
       <c r="F24" s="3">
-        <v>345200</v>
+        <v>364800</v>
       </c>
       <c r="G24" s="3">
-        <v>293300</v>
+        <v>370900</v>
       </c>
       <c r="H24" s="3">
-        <v>304600</v>
+        <v>299000</v>
       </c>
       <c r="I24" s="3">
-        <v>256600</v>
+        <v>312500</v>
       </c>
       <c r="J24" s="3">
+        <v>269700</v>
+      </c>
+      <c r="K24" s="3">
         <v>281700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>284300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>271600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>211100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>130800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>97800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>76600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1200800</v>
+        <v>1253000</v>
       </c>
       <c r="E26" s="3">
-        <v>1079200</v>
+        <v>1205900</v>
       </c>
       <c r="F26" s="3">
-        <v>1007800</v>
+        <v>1067900</v>
       </c>
       <c r="G26" s="3">
-        <v>822900</v>
+        <v>1082800</v>
       </c>
       <c r="H26" s="3">
-        <v>929900</v>
+        <v>839000</v>
       </c>
       <c r="I26" s="3">
-        <v>840200</v>
+        <v>954200</v>
       </c>
       <c r="J26" s="3">
+        <v>883000</v>
+      </c>
+      <c r="K26" s="3">
         <v>762000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>791200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>756400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>670100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>346900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>97900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>336600</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1200800</v>
+        <v>1253000</v>
       </c>
       <c r="E27" s="3">
-        <v>1079200</v>
+        <v>1205900</v>
       </c>
       <c r="F27" s="3">
-        <v>1007800</v>
+        <v>1067900</v>
       </c>
       <c r="G27" s="3">
-        <v>822900</v>
+        <v>1082800</v>
       </c>
       <c r="H27" s="3">
-        <v>929900</v>
+        <v>839000</v>
       </c>
       <c r="I27" s="3">
-        <v>840200</v>
+        <v>954200</v>
       </c>
       <c r="J27" s="3">
+        <v>883000</v>
+      </c>
+      <c r="K27" s="3">
         <v>762000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>791200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>756400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>670100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>346900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>97900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>336400</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,32 +1784,35 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>41600</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-6100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-13100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-8900</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1763,54 +1832,60 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1200800</v>
+        <v>1253000</v>
       </c>
       <c r="E33" s="3">
-        <v>1079200</v>
+        <v>1205900</v>
       </c>
       <c r="F33" s="3">
-        <v>1007800</v>
+        <v>1067900</v>
       </c>
       <c r="G33" s="3">
-        <v>822900</v>
+        <v>1082800</v>
       </c>
       <c r="H33" s="3">
-        <v>929900</v>
+        <v>839000</v>
       </c>
       <c r="I33" s="3">
-        <v>840200</v>
+        <v>954200</v>
       </c>
       <c r="J33" s="3">
+        <v>883000</v>
+      </c>
+      <c r="K33" s="3">
         <v>762000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>791200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>756400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>670100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>346900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>97900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>336400</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1200800</v>
+        <v>1253000</v>
       </c>
       <c r="E35" s="3">
-        <v>1079200</v>
+        <v>1205900</v>
       </c>
       <c r="F35" s="3">
-        <v>1007800</v>
+        <v>1067900</v>
       </c>
       <c r="G35" s="3">
-        <v>822900</v>
+        <v>1082800</v>
       </c>
       <c r="H35" s="3">
-        <v>929900</v>
+        <v>839000</v>
       </c>
       <c r="I35" s="3">
-        <v>840200</v>
+        <v>954200</v>
       </c>
       <c r="J35" s="3">
+        <v>883000</v>
+      </c>
+      <c r="K35" s="3">
         <v>762000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>791200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>756400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>670100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>346900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>97900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>336400</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44469</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44104</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43738</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43373</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43008</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42643</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42277</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41912</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41547</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41182</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40816</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,80 +2072,84 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1154400</v>
+        <v>1081600</v>
       </c>
       <c r="E41" s="3">
-        <v>711400</v>
+        <v>1159300</v>
       </c>
       <c r="F41" s="3">
-        <v>1250800</v>
+        <v>703900</v>
       </c>
       <c r="G41" s="3">
-        <v>1257300</v>
+        <v>1343900</v>
       </c>
       <c r="H41" s="3">
-        <v>157400</v>
+        <v>1281900</v>
       </c>
       <c r="I41" s="3">
-        <v>135500</v>
+        <v>161500</v>
       </c>
       <c r="J41" s="3">
+        <v>142400</v>
+      </c>
+      <c r="K41" s="3">
         <v>122100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>441600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>236200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>417700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>107200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>177000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>104600</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>58900</v>
-      </c>
-      <c r="E42" s="3" t="s">
+        <v>2400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F42" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G42" s="3">
+        <v>1600</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I42" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2068,332 +2157,356 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>143000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>163500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>7800</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1155800</v>
+        <v>1946600</v>
       </c>
       <c r="E43" s="3">
-        <v>1076800</v>
+        <v>1903400</v>
       </c>
       <c r="F43" s="3">
-        <v>910100</v>
+        <v>1865000</v>
       </c>
       <c r="G43" s="3">
-        <v>919200</v>
+        <v>1804400</v>
       </c>
       <c r="H43" s="3">
-        <v>1006500</v>
+        <v>1744200</v>
       </c>
       <c r="I43" s="3">
-        <v>1093900</v>
+        <v>1860700</v>
       </c>
       <c r="J43" s="3">
+        <v>1878900</v>
+      </c>
+      <c r="K43" s="3">
         <v>951400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>821400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>853900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>814400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1706200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2175800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>380100</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>841900</v>
-      </c>
-      <c r="E44" s="3">
-        <v>877300</v>
-      </c>
-      <c r="F44" s="3">
-        <v>769300</v>
-      </c>
-      <c r="G44" s="3">
-        <v>791500</v>
-      </c>
-      <c r="H44" s="3">
-        <v>806800</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
+        <v>679100</v>
+      </c>
+      <c r="L44" s="3">
+        <v>692600</v>
+      </c>
+      <c r="M44" s="3">
+        <v>675600</v>
+      </c>
+      <c r="N44" s="3">
+        <v>630000</v>
+      </c>
+      <c r="O44" s="3">
         <v>694000</v>
       </c>
-      <c r="J44" s="3">
-        <v>679100</v>
-      </c>
-      <c r="K44" s="3">
-        <v>692600</v>
-      </c>
-      <c r="L44" s="3">
-        <v>675600</v>
-      </c>
-      <c r="M44" s="3">
-        <v>630000</v>
-      </c>
-      <c r="N44" s="3">
-        <v>694000</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1072900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>300400</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>420800</v>
+        <v>378900</v>
       </c>
       <c r="E45" s="3">
-        <v>535900</v>
+        <v>432300</v>
       </c>
       <c r="F45" s="3">
-        <v>577500</v>
+        <v>456300</v>
       </c>
       <c r="G45" s="3">
-        <v>665500</v>
+        <v>482500</v>
       </c>
       <c r="H45" s="3">
-        <v>427100</v>
+        <v>557100</v>
       </c>
       <c r="I45" s="3">
-        <v>361800</v>
+        <v>300800</v>
       </c>
       <c r="J45" s="3">
+        <v>261400</v>
+      </c>
+      <c r="K45" s="3">
         <v>354900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>416200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>528900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>373700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>503800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>508400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>267400</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>3631800</v>
+        <v>3565900</v>
       </c>
       <c r="E46" s="3">
-        <v>3201400</v>
+        <v>3647200</v>
       </c>
       <c r="F46" s="3">
-        <v>3507700</v>
+        <v>3167700</v>
       </c>
       <c r="G46" s="3">
-        <v>3633400</v>
+        <v>3768800</v>
       </c>
       <c r="H46" s="3">
-        <v>2397800</v>
+        <v>3704700</v>
       </c>
       <c r="I46" s="3">
-        <v>2285200</v>
+        <v>2460600</v>
       </c>
       <c r="J46" s="3">
+        <v>2401600</v>
+      </c>
+      <c r="K46" s="3">
         <v>2107500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2371900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2294600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2235800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2042100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2021200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1060300</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>27900</v>
+        <v>17900</v>
       </c>
       <c r="E47" s="3">
-        <v>20200</v>
+        <v>12700</v>
       </c>
       <c r="F47" s="3">
-        <v>112400</v>
+        <v>12300</v>
       </c>
       <c r="G47" s="3">
-        <v>115300</v>
+        <v>15300</v>
       </c>
       <c r="H47" s="3">
-        <v>130200</v>
+        <v>17000</v>
       </c>
       <c r="I47" s="3">
-        <v>86700</v>
+        <v>18600</v>
       </c>
       <c r="J47" s="3">
+        <v>23200</v>
+      </c>
+      <c r="K47" s="3">
         <v>81900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>95800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>241500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>187600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>165100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>29400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>35600</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>641600</v>
+        <v>616600</v>
       </c>
       <c r="E48" s="3">
-        <v>666000</v>
+        <v>644300</v>
       </c>
       <c r="F48" s="3">
-        <v>690700</v>
+        <v>659000</v>
       </c>
       <c r="G48" s="3">
-        <v>765400</v>
+        <v>742100</v>
       </c>
       <c r="H48" s="3">
-        <v>292700</v>
+        <v>780400</v>
       </c>
       <c r="I48" s="3">
-        <v>285700</v>
+        <v>300400</v>
       </c>
       <c r="J48" s="3">
+        <v>300200</v>
+      </c>
+      <c r="K48" s="3">
         <v>292000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>325200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>366100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>379600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>361600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>731200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>384000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7107900</v>
+        <v>7542100</v>
       </c>
       <c r="E49" s="3">
-        <v>6889300</v>
+        <v>6910000</v>
       </c>
       <c r="F49" s="3">
-        <v>6534500</v>
+        <v>6626200</v>
       </c>
       <c r="G49" s="3">
-        <v>6728600</v>
+        <v>6838500</v>
       </c>
       <c r="H49" s="3">
-        <v>6263400</v>
+        <v>6681000</v>
       </c>
       <c r="I49" s="3">
-        <v>5936100</v>
+        <v>6258900</v>
       </c>
       <c r="J49" s="3">
+        <v>6050400</v>
+      </c>
+      <c r="K49" s="3">
         <v>5736900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5666800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5962400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5645900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6051100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10341600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2561900</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>221000</v>
+        <v>172500</v>
       </c>
       <c r="E52" s="3">
-        <v>394000</v>
+        <v>157500</v>
       </c>
       <c r="F52" s="3">
-        <v>211900</v>
+        <v>333000</v>
       </c>
       <c r="G52" s="3">
-        <v>204100</v>
+        <v>254900</v>
       </c>
       <c r="H52" s="3">
-        <v>206900</v>
+        <v>220900</v>
       </c>
       <c r="I52" s="3">
-        <v>180100</v>
+        <v>248500</v>
       </c>
       <c r="J52" s="3">
+        <v>146600</v>
+      </c>
+      <c r="K52" s="3">
         <v>170600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>197600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>255900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>310000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>351500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>535600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42600</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>11630200</v>
+        <v>12350900</v>
       </c>
       <c r="E54" s="3">
-        <v>11170800</v>
+        <v>11679500</v>
       </c>
       <c r="F54" s="3">
-        <v>11057100</v>
+        <v>11053100</v>
       </c>
       <c r="G54" s="3">
-        <v>11446800</v>
+        <v>11880100</v>
       </c>
       <c r="H54" s="3">
-        <v>9291000</v>
+        <v>11671400</v>
       </c>
       <c r="I54" s="3">
-        <v>8773700</v>
+        <v>9534200</v>
       </c>
       <c r="J54" s="3">
+        <v>9220600</v>
+      </c>
+      <c r="K54" s="3">
         <v>8388900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8657300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9120400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8758900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8280100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7955800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3577900</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>680700</v>
+        <v>740100</v>
       </c>
       <c r="E57" s="3">
-        <v>748200</v>
+        <v>683500</v>
       </c>
       <c r="F57" s="3">
-        <v>656100</v>
+        <v>740300</v>
       </c>
       <c r="G57" s="3">
-        <v>755200</v>
+        <v>705000</v>
       </c>
       <c r="H57" s="3">
-        <v>816300</v>
+        <v>611000</v>
       </c>
       <c r="I57" s="3">
-        <v>835300</v>
+        <v>837600</v>
       </c>
       <c r="J57" s="3">
+        <v>877900</v>
+      </c>
+      <c r="K57" s="3">
         <v>739300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>820200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>861700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>826700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>851700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1817900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>233300</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>999500</v>
+        <v>112000</v>
       </c>
       <c r="E58" s="3">
-        <v>185100</v>
+        <v>1005400</v>
       </c>
       <c r="F58" s="3">
-        <v>412600</v>
+        <v>183100</v>
       </c>
       <c r="G58" s="3">
-        <v>360300</v>
+        <v>447900</v>
       </c>
       <c r="H58" s="3">
-        <v>83600</v>
+        <v>371400</v>
       </c>
       <c r="I58" s="3">
-        <v>256600</v>
+        <v>88000</v>
       </c>
       <c r="J58" s="3">
+        <v>286600</v>
+      </c>
+      <c r="K58" s="3">
         <v>90100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>142200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>178700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>62700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>406600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>77900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>746400</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1739700</v>
+        <v>903300</v>
       </c>
       <c r="E59" s="3">
-        <v>1753100</v>
+        <v>931900</v>
       </c>
       <c r="F59" s="3">
-        <v>1731000</v>
+        <v>911000</v>
       </c>
       <c r="G59" s="3">
-        <v>1575600</v>
+        <v>997900</v>
       </c>
       <c r="H59" s="3">
-        <v>1223200</v>
+        <v>1097500</v>
       </c>
       <c r="I59" s="3">
-        <v>1204500</v>
+        <v>767300</v>
       </c>
       <c r="J59" s="3">
+        <v>783000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1159200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1094800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1364300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1276700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1391900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2383800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>495800</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3419800</v>
+        <v>2627100</v>
       </c>
       <c r="E60" s="3">
-        <v>2686300</v>
+        <v>3434300</v>
       </c>
       <c r="F60" s="3">
-        <v>2799800</v>
+        <v>2658000</v>
       </c>
       <c r="G60" s="3">
-        <v>2691100</v>
+        <v>3008200</v>
       </c>
       <c r="H60" s="3">
-        <v>2123000</v>
+        <v>2743900</v>
       </c>
       <c r="I60" s="3">
-        <v>2296400</v>
+        <v>2178600</v>
       </c>
       <c r="J60" s="3">
+        <v>2413400</v>
+      </c>
+      <c r="K60" s="3">
         <v>1988600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2057200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2404600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2166100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2650100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2249400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1475400</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1755200</v>
+        <v>2344000</v>
       </c>
       <c r="E61" s="3">
-        <v>2741900</v>
+        <v>1762700</v>
       </c>
       <c r="F61" s="3">
-        <v>2663300</v>
+        <v>2714200</v>
       </c>
       <c r="G61" s="3">
-        <v>2925300</v>
+        <v>2893100</v>
       </c>
       <c r="H61" s="3">
-        <v>1632500</v>
+        <v>3021900</v>
       </c>
       <c r="I61" s="3">
-        <v>1069100</v>
+        <v>1687700</v>
       </c>
       <c r="J61" s="3">
+        <v>1163000</v>
+      </c>
+      <c r="K61" s="3">
         <v>1280500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1272600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1467200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2026600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1775100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2378500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>84300</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>337800</v>
+        <v>142700</v>
       </c>
       <c r="E62" s="3">
-        <v>389000</v>
+        <v>112500</v>
       </c>
       <c r="F62" s="3">
-        <v>451400</v>
+        <v>90300</v>
       </c>
       <c r="G62" s="3">
-        <v>483200</v>
+        <v>140400</v>
       </c>
       <c r="H62" s="3">
-        <v>468000</v>
+        <v>136500</v>
       </c>
       <c r="I62" s="3">
-        <v>487500</v>
+        <v>133900</v>
       </c>
       <c r="J62" s="3">
+        <v>141200</v>
+      </c>
+      <c r="K62" s="3">
         <v>553900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>541300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>542500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>676600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>768100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1604300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>401400</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5512900</v>
+        <v>5372100</v>
       </c>
       <c r="E66" s="3">
-        <v>5817300</v>
+        <v>5536300</v>
       </c>
       <c r="F66" s="3">
-        <v>5914500</v>
+        <v>5756000</v>
       </c>
       <c r="G66" s="3">
-        <v>6099600</v>
+        <v>6354700</v>
       </c>
       <c r="H66" s="3">
-        <v>4223500</v>
+        <v>6219200</v>
       </c>
       <c r="I66" s="3">
-        <v>3853000</v>
+        <v>4334100</v>
       </c>
       <c r="J66" s="3">
+        <v>4049200</v>
+      </c>
+      <c r="K66" s="3">
         <v>3823100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3871100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4414300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4869300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5193400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5408400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1773200</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4658900</v>
+        <v>5277300</v>
       </c>
       <c r="E72" s="3">
-        <v>3993400</v>
+        <v>4678700</v>
       </c>
       <c r="F72" s="3">
-        <v>3483400</v>
+        <v>3951300</v>
       </c>
       <c r="G72" s="3">
-        <v>3462400</v>
+        <v>3742700</v>
       </c>
       <c r="H72" s="3">
-        <v>3355100</v>
+        <v>3530300</v>
       </c>
       <c r="I72" s="3">
-        <v>3129500</v>
+        <v>3442900</v>
       </c>
       <c r="J72" s="3">
+        <v>3288900</v>
+      </c>
+      <c r="K72" s="3">
         <v>2793100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2797700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2365800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1836900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1181200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1656900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>812500</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>6117300</v>
+        <v>6978800</v>
       </c>
       <c r="E76" s="3">
-        <v>5353500</v>
+        <v>6143300</v>
       </c>
       <c r="F76" s="3">
-        <v>5142600</v>
+        <v>5297200</v>
       </c>
       <c r="G76" s="3">
-        <v>5347200</v>
+        <v>5525400</v>
       </c>
       <c r="H76" s="3">
-        <v>5067500</v>
+        <v>5452100</v>
       </c>
       <c r="I76" s="3">
-        <v>4920800</v>
+        <v>5200100</v>
       </c>
       <c r="J76" s="3">
+        <v>5171400</v>
+      </c>
+      <c r="K76" s="3">
         <v>4565800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4786100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4706100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3889600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3086800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2547400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1804700</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44469</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44104</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43738</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43373</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43008</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42643</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42277</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41912</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41547</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41182</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40816</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1200800</v>
+        <v>1253000</v>
       </c>
       <c r="E81" s="3">
-        <v>1079200</v>
+        <v>1205900</v>
       </c>
       <c r="F81" s="3">
-        <v>1007800</v>
+        <v>1067900</v>
       </c>
       <c r="G81" s="3">
-        <v>822900</v>
+        <v>1082800</v>
       </c>
       <c r="H81" s="3">
-        <v>929900</v>
+        <v>839000</v>
       </c>
       <c r="I81" s="3">
-        <v>840200</v>
+        <v>954200</v>
       </c>
       <c r="J81" s="3">
+        <v>883000</v>
+      </c>
+      <c r="K81" s="3">
         <v>762000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>791200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>756400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>670100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>346900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>97900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>336400</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>373500</v>
+        <v>193500</v>
       </c>
       <c r="E83" s="3">
-        <v>343400</v>
+        <v>211700</v>
       </c>
       <c r="F83" s="3">
-        <v>371000</v>
+        <v>200300</v>
       </c>
       <c r="G83" s="3">
-        <v>416400</v>
+        <v>241000</v>
       </c>
       <c r="H83" s="3">
-        <v>288800</v>
+        <v>243800</v>
       </c>
       <c r="I83" s="3">
-        <v>289100</v>
+        <v>120300</v>
       </c>
       <c r="J83" s="3">
+        <v>121100</v>
+      </c>
+      <c r="K83" s="3">
         <v>277700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>296200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>328100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>346400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>331800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>172200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>171600</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1554800</v>
+        <v>1632200</v>
       </c>
       <c r="E89" s="3">
-        <v>1372800</v>
+        <v>1561400</v>
       </c>
       <c r="F89" s="3">
-        <v>1557600</v>
+        <v>1358400</v>
       </c>
       <c r="G89" s="3">
-        <v>1427000</v>
+        <v>1673500</v>
       </c>
       <c r="H89" s="3">
-        <v>1202700</v>
+        <v>1455000</v>
       </c>
       <c r="I89" s="3">
-        <v>1099300</v>
+        <v>1234200</v>
       </c>
       <c r="J89" s="3">
+        <v>1155300</v>
+      </c>
+      <c r="K89" s="3">
         <v>1000000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>987000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>997600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>916000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>510900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>456400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>437900</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-117600</v>
+        <v>-81200</v>
       </c>
       <c r="E91" s="3">
-        <v>-114900</v>
+        <v>-118100</v>
       </c>
       <c r="F91" s="3">
-        <v>-89700</v>
+        <v>-113700</v>
       </c>
       <c r="G91" s="3">
-        <v>-94600</v>
+        <v>-96300</v>
       </c>
       <c r="H91" s="3">
-        <v>-119300</v>
+        <v>-96400</v>
       </c>
       <c r="I91" s="3">
-        <v>-105400</v>
+        <v>-122400</v>
       </c>
       <c r="J91" s="3">
+        <v>-110800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-82900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-122500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-94800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-141500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-108000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-48000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-413600</v>
+        <v>-574000</v>
       </c>
       <c r="E94" s="3">
-        <v>-671300</v>
+        <v>-415300</v>
       </c>
       <c r="F94" s="3">
-        <v>-292600</v>
+        <v>-664200</v>
       </c>
       <c r="G94" s="3">
-        <v>-421400</v>
+        <v>-307300</v>
       </c>
       <c r="H94" s="3">
-        <v>-699900</v>
+        <v>-429700</v>
       </c>
       <c r="I94" s="3">
-        <v>-425000</v>
+        <v>-718200</v>
       </c>
       <c r="J94" s="3">
+        <v>-446700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-436000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-283400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-199000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-250400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-178000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2120300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100600</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,8 +4453,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4265,9 +4498,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-877700</v>
+        <v>-1190000</v>
       </c>
       <c r="E100" s="3">
-        <v>-1171200</v>
+        <v>-881400</v>
       </c>
       <c r="F100" s="3">
-        <v>-1217000</v>
+        <v>-1158900</v>
       </c>
       <c r="G100" s="3">
-        <v>69300</v>
+        <v>-1409800</v>
       </c>
       <c r="H100" s="3">
-        <v>-463100</v>
+        <v>70700</v>
       </c>
       <c r="I100" s="3">
-        <v>-647100</v>
+        <v>-475200</v>
       </c>
       <c r="J100" s="3">
+        <v>-680000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-870800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-493300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1008700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-322800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-339400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1700900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-377700</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>6500</v>
+        <v>25700</v>
       </c>
       <c r="E101" s="3">
-        <v>-34200</v>
+        <v>6600</v>
       </c>
       <c r="F101" s="3">
-        <v>-54400</v>
+        <v>-33900</v>
       </c>
       <c r="G101" s="3">
-        <v>24900</v>
+        <v>-58400</v>
       </c>
       <c r="H101" s="3">
-        <v>-17900</v>
+        <v>25400</v>
       </c>
       <c r="I101" s="3">
-        <v>-13800</v>
+        <v>-18300</v>
       </c>
       <c r="J101" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="K101" s="3">
         <v>-10300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>5400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>31700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3700</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>270100</v>
+        <v>-106100</v>
       </c>
       <c r="E102" s="3">
-        <v>-503900</v>
+        <v>271200</v>
       </c>
       <c r="F102" s="3">
-        <v>-6500</v>
+        <v>-498600</v>
       </c>
       <c r="G102" s="3">
-        <v>1099900</v>
+        <v>-102000</v>
       </c>
       <c r="H102" s="3">
-        <v>21900</v>
+        <v>1121400</v>
       </c>
       <c r="I102" s="3">
-        <v>13400</v>
+        <v>22500</v>
       </c>
       <c r="J102" s="3">
+        <v>14100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-317000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>215600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-178300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>334900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>39000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GIB_YR_FIN.xlsx
@@ -777,25 +777,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>7574200</v>
+        <v>8637500</v>
       </c>
       <c r="E9" s="3">
-        <v>7330700</v>
+        <v>8440000</v>
       </c>
       <c r="F9" s="3">
-        <v>6413100</v>
+        <v>7476000</v>
       </c>
       <c r="G9" s="3">
-        <v>6616900</v>
+        <v>7615500</v>
       </c>
       <c r="H9" s="3">
-        <v>6249500</v>
+        <v>7266500</v>
       </c>
       <c r="I9" s="3">
-        <v>6344700</v>
+        <v>7432400</v>
       </c>
       <c r="J9" s="3">
-        <v>6180700</v>
+        <v>7240000</v>
       </c>
       <c r="K9" s="3">
         <v>827500</v>
@@ -825,25 +825,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3289300</v>
+        <v>2226100</v>
       </c>
       <c r="E10" s="3">
-        <v>3237700</v>
+        <v>2128400</v>
       </c>
       <c r="F10" s="3">
-        <v>2958800</v>
+        <v>1895900</v>
       </c>
       <c r="G10" s="3">
-        <v>2974200</v>
+        <v>1975600</v>
       </c>
       <c r="H10" s="3">
-        <v>2880300</v>
+        <v>1863300</v>
       </c>
       <c r="I10" s="3">
-        <v>2803900</v>
+        <v>1716200</v>
       </c>
       <c r="J10" s="3">
-        <v>2721000</v>
+        <v>1661600</v>
       </c>
       <c r="K10" s="3">
         <v>7155700</v>
